--- a/Manuscript Variant Workbooks/CulFf1.24-to-Queens214_scribe-2_MS-spreadsheet.xlsx
+++ b/Manuscript Variant Workbooks/CulFf1.24-to-Queens214_scribe-2_MS-spreadsheet.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/186593bc330ab858/Cambridge PhD/Thesis/8 Corrections/Files to Upload/To Github/Manuscript Variant Workbooks/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/186593bc330ab858/Cambridge PhD/Thesis/10 The Final Final Version/New and Updated Files for Upload/MS Variant Spreadsheets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="487" documentId="8_{2A16B1EB-A06F-402C-AF69-EDB4188A444D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF97CF33-17E9-4CE4-8BFA-945D84BB25A8}"/>
+  <xr:revisionPtr revIDLastSave="519" documentId="8_{2A16B1EB-A06F-402C-AF69-EDB4188A444D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{316B22FC-82EA-494E-AF13-C504E1167A5C}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{5BB4D106-A247-41F8-A104-83D51E35EC09}"/>
   </bookViews>
@@ -32,7 +32,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">AddOmits!$A$1:$AH$43</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Gen-filters'!$A$1:$AG$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Gen-filters'!$A$1:$AG$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Unfiltered Data'!$A$1:$AL$114</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">WF_AO_HM!$A$1:$AH$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">WF_AO_LM!$A$1:$AH$35</definedName>
@@ -2774,6 +2774,13 @@
     <author>tc={76FAFAD1-6EC0-4A30-9ACB-812427CB477E}</author>
     <author>tc={3F3DE51F-E097-4542-8820-9D77317020A4}</author>
     <author>tc={FEF04B0C-A8B3-467D-A075-DE68F3219A8F}</author>
+    <author>tc={2CF52AFD-CF13-43C6-AE65-1932FB2EB6D6}</author>
+    <author>tc={21F00353-2015-4D13-8645-46E303C433F1}</author>
+    <author>tc={D0F8D6BD-068D-4303-9C66-A12845C898DE}</author>
+    <author>tc={91566328-4150-49AD-9102-B38078C2A212}</author>
+    <author>tc={C119846B-5B2A-4856-9CFB-216AD7D71EBB}</author>
+    <author>tc={48C6D0FD-C6F8-45F8-B647-860ADD900CBF}</author>
+    <author>tc={0D18526A-8833-4BFE-A5AB-CA0051C886F9}</author>
   </authors>
   <commentList>
     <comment ref="B1" authorId="0" shapeId="0" xr:uid="{2E29B512-4B73-4E22-ABD5-7D99061F14FC}">
@@ -3179,7 +3186,7 @@
     For substitutions, the word frequency of the autograph reading</t>
       </text>
     </comment>
-    <comment ref="W1" authorId="0" shapeId="0" xr:uid="{19E6B7B9-A2A5-41A0-9A6D-365238A748E8}">
+    <comment ref="X1" authorId="0" shapeId="0" xr:uid="{19E6B7B9-A2A5-41A0-9A6D-365238A748E8}">
       <text>
         <r>
           <rPr>
@@ -3203,7 +3210,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X1" authorId="0" shapeId="0" xr:uid="{951832B1-FCD9-4F1A-96AC-367D4C48761E}">
+    <comment ref="Y1" authorId="0" shapeId="0" xr:uid="{951832B1-FCD9-4F1A-96AC-367D4C48761E}">
       <text>
         <r>
           <rPr>
@@ -3227,7 +3234,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y1" authorId="0" shapeId="0" xr:uid="{B867E4BC-6ACE-4DB8-A204-C88C06407647}">
+    <comment ref="Z1" authorId="0" shapeId="0" xr:uid="{B867E4BC-6ACE-4DB8-A204-C88C06407647}">
       <text>
         <r>
           <rPr>
@@ -3251,7 +3258,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z1" authorId="0" shapeId="0" xr:uid="{592A2388-B21E-4881-83E9-894E7CF41411}">
+    <comment ref="AA1" authorId="0" shapeId="0" xr:uid="{592A2388-B21E-4881-83E9-894E7CF41411}">
       <text>
         <r>
           <rPr>
@@ -3275,7 +3282,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AB1" authorId="0" shapeId="0" xr:uid="{F3D13D34-3C4D-4B9F-9B5B-8F7004EAFE33}">
+    <comment ref="AC1" authorId="0" shapeId="0" xr:uid="{F3D13D34-3C4D-4B9F-9B5B-8F7004EAFE33}">
       <text>
         <r>
           <rPr>
@@ -3300,7 +3307,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AC1" authorId="0" shapeId="0" xr:uid="{39705D0E-6B11-4254-88BE-95CF831F2AF9}">
+    <comment ref="AD1" authorId="0" shapeId="0" xr:uid="{39705D0E-6B11-4254-88BE-95CF831F2AF9}">
       <text>
         <r>
           <rPr>
@@ -3324,7 +3331,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AD1" authorId="0" shapeId="0" xr:uid="{2509ECB3-C9BD-4043-8B0C-C97DDCC4BE0A}">
+    <comment ref="AE1" authorId="0" shapeId="0" xr:uid="{2509ECB3-C9BD-4043-8B0C-C97DDCC4BE0A}">
       <text>
         <r>
           <rPr>
@@ -3365,6 +3372,62 @@
       </text>
     </comment>
     <comment ref="D7" authorId="5" shapeId="0" xr:uid="{FEF04B0C-A8B3-467D-A075-DE68F3219A8F}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    The ratio of harmonizations to disharmonizations; = harmonizations / (harmonizations + disharmonizations)</t>
+      </text>
+    </comment>
+    <comment ref="E11" authorId="6" shapeId="0" xr:uid="{2CF52AFD-CF13-43C6-AE65-1932FB2EB6D6}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    All cases where influence from preceding material was possible.</t>
+      </text>
+    </comment>
+    <comment ref="F11" authorId="7" shapeId="0" xr:uid="{21F00353-2015-4D13-8645-46E303C433F1}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    All cases where influence from following material was possible.</t>
+      </text>
+    </comment>
+    <comment ref="G11" authorId="8" shapeId="0" xr:uid="{D0F8D6BD-068D-4303-9C66-A12845C898DE}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Only cases where verbal parallels existed both behind and after the variant in question and the direction of change in verbal similarity was the same.</t>
+      </text>
+    </comment>
+    <comment ref="H11" authorId="9" shapeId="0" xr:uid="{91566328-4150-49AD-9102-B38078C2A212}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    All potential cases of verbal harmonization/disharmonization, forward and backward.</t>
+      </text>
+    </comment>
+    <comment ref="D12" authorId="10" shapeId="0" xr:uid="{C119846B-5B2A-4856-9CFB-216AD7D71EBB}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    The number of variants that harmonized to parallel phrases in the near context</t>
+      </text>
+    </comment>
+    <comment ref="D13" authorId="11" shapeId="0" xr:uid="{48C6D0FD-C6F8-45F8-B647-860ADD900CBF}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    The number of variants that disharmonized from  parallel phrases in the near context</t>
+      </text>
+    </comment>
+    <comment ref="D14" authorId="12" shapeId="0" xr:uid="{0D18526A-8833-4BFE-A5AB-CA0051C886F9}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -3536,7 +3599,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K3" authorId="1" shapeId="0" xr:uid="{3B3C42D7-D23A-4A13-961D-A51B33C4F812}">
+    <comment ref="L3" authorId="1" shapeId="0" xr:uid="{3B3C42D7-D23A-4A13-961D-A51B33C4F812}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -3544,7 +3607,7 @@
     The apograph reading is singular and the autograph reading is not. The singular readings method would detect this variant</t>
       </text>
     </comment>
-    <comment ref="K4" authorId="2" shapeId="0" xr:uid="{33503B61-D396-4CB6-B78C-738CF807F495}">
+    <comment ref="L4" authorId="2" shapeId="0" xr:uid="{33503B61-D396-4CB6-B78C-738CF807F495}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -3552,7 +3615,7 @@
     That is, the autograph contains a singular reading and the apograph followed it</t>
       </text>
     </comment>
-    <comment ref="K5" authorId="3" shapeId="0" xr:uid="{578F9A70-DB86-4124-99A3-FB5E8B3F24F9}">
+    <comment ref="L5" authorId="3" shapeId="0" xr:uid="{578F9A70-DB86-4124-99A3-FB5E8B3F24F9}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -3560,7 +3623,7 @@
     The apograph reading is not singular: other witnesses contain the same reading. These are real variants produced by the apograph scribe, but the singular readings method would not detect them</t>
       </text>
     </comment>
-    <comment ref="M13" authorId="4" shapeId="0" xr:uid="{CA332D3B-255C-4BFE-A327-192CC1243DCB}">
+    <comment ref="N13" authorId="4" shapeId="0" xr:uid="{CA332D3B-255C-4BFE-A327-192CC1243DCB}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -7209,6 +7272,13 @@
     <author>tc={40BA1C46-D4FA-48E4-AC15-E2EEAF6EB295}</author>
     <author>tc={23BFB271-F88E-4353-BA05-D7370260B9D2}</author>
     <author>tc={0AD6D9F9-2F1D-44BE-A953-FBE9B8E07C12}</author>
+    <author>tc={ED08F7F9-1454-4A27-8E33-0D39A1CDAA02}</author>
+    <author>tc={0AF28895-093D-4DC8-A63F-A8A5D20CF2B3}</author>
+    <author>tc={3974ECD3-1AA7-4B3E-80B0-1A60B8E1FB87}</author>
+    <author>tc={AD3C4D56-9A0A-4345-8005-6EA35E72C7A6}</author>
+    <author>tc={97DB7EF9-2486-4788-9B63-6F2F6CB3C1B9}</author>
+    <author>tc={AC9053CF-3511-46F8-956C-335082D56E88}</author>
+    <author>tc={68D9F6CF-BCFD-4577-9BE7-71C6F178CB12}</author>
   </authors>
   <commentList>
     <comment ref="B1" authorId="0" shapeId="0" xr:uid="{9B5C5FCE-24E5-4C07-87B2-DF43D673457F}">
@@ -7614,7 +7684,7 @@
     For substitutions, the word frequency of the autograph reading</t>
       </text>
     </comment>
-    <comment ref="W1" authorId="0" shapeId="0" xr:uid="{A2550B7D-ADA8-43ED-A3E5-60D829F249D1}">
+    <comment ref="X1" authorId="0" shapeId="0" xr:uid="{A2550B7D-ADA8-43ED-A3E5-60D829F249D1}">
       <text>
         <r>
           <rPr>
@@ -7638,7 +7708,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X1" authorId="0" shapeId="0" xr:uid="{6ADCD08D-845B-47F3-B298-29BEB8B2D3FB}">
+    <comment ref="Y1" authorId="0" shapeId="0" xr:uid="{6ADCD08D-845B-47F3-B298-29BEB8B2D3FB}">
       <text>
         <r>
           <rPr>
@@ -7662,7 +7732,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y1" authorId="0" shapeId="0" xr:uid="{4B655A68-77C2-4560-9EAF-47782555D6D2}">
+    <comment ref="Z1" authorId="0" shapeId="0" xr:uid="{4B655A68-77C2-4560-9EAF-47782555D6D2}">
       <text>
         <r>
           <rPr>
@@ -7686,7 +7756,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z1" authorId="0" shapeId="0" xr:uid="{769FF9A5-4288-469C-A839-434E67C88244}">
+    <comment ref="AA1" authorId="0" shapeId="0" xr:uid="{769FF9A5-4288-469C-A839-434E67C88244}">
       <text>
         <r>
           <rPr>
@@ -7710,7 +7780,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AB1" authorId="0" shapeId="0" xr:uid="{7EA34E82-A41B-4B07-8303-E1DE378F26D3}">
+    <comment ref="AC1" authorId="0" shapeId="0" xr:uid="{7EA34E82-A41B-4B07-8303-E1DE378F26D3}">
       <text>
         <r>
           <rPr>
@@ -7735,7 +7805,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AC1" authorId="0" shapeId="0" xr:uid="{EDBE7777-3BA0-4C5B-BC77-4438DCFA980A}">
+    <comment ref="AD1" authorId="0" shapeId="0" xr:uid="{EDBE7777-3BA0-4C5B-BC77-4438DCFA980A}">
       <text>
         <r>
           <rPr>
@@ -7759,7 +7829,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AD1" authorId="0" shapeId="0" xr:uid="{07BD5970-A660-4292-AB06-66E2FA46AF26}">
+    <comment ref="AE1" authorId="0" shapeId="0" xr:uid="{07BD5970-A660-4292-AB06-66E2FA46AF26}">
       <text>
         <r>
           <rPr>
@@ -7800,6 +7870,62 @@
       </text>
     </comment>
     <comment ref="D7" authorId="5" shapeId="0" xr:uid="{0AD6D9F9-2F1D-44BE-A953-FBE9B8E07C12}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    The ratio of harmonizations to disharmonizations; = harmonizations / (harmonizations + disharmonizations)</t>
+      </text>
+    </comment>
+    <comment ref="E11" authorId="6" shapeId="0" xr:uid="{ED08F7F9-1454-4A27-8E33-0D39A1CDAA02}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    All cases where influence from preceding material was possible.</t>
+      </text>
+    </comment>
+    <comment ref="F11" authorId="7" shapeId="0" xr:uid="{0AF28895-093D-4DC8-A63F-A8A5D20CF2B3}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    All cases where influence from following material was possible.</t>
+      </text>
+    </comment>
+    <comment ref="G11" authorId="8" shapeId="0" xr:uid="{3974ECD3-1AA7-4B3E-80B0-1A60B8E1FB87}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Only cases where verbal parallels existed both behind and after the variant in question and the direction of change in verbal similarity was the same.</t>
+      </text>
+    </comment>
+    <comment ref="H11" authorId="9" shapeId="0" xr:uid="{AD3C4D56-9A0A-4345-8005-6EA35E72C7A6}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    All potential cases of verbal harmonization/disharmonization, forward and backward.</t>
+      </text>
+    </comment>
+    <comment ref="D12" authorId="10" shapeId="0" xr:uid="{97DB7EF9-2486-4788-9B63-6F2F6CB3C1B9}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    The number of variants that harmonized to parallel phrases in the near context</t>
+      </text>
+    </comment>
+    <comment ref="D13" authorId="11" shapeId="0" xr:uid="{AC9053CF-3511-46F8-956C-335082D56E88}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    The number of variants that disharmonized from  parallel phrases in the near context</t>
+      </text>
+    </comment>
+    <comment ref="D14" authorId="12" shapeId="0" xr:uid="{68D9F6CF-BCFD-4577-9BE7-71C6F178CB12}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -9389,7 +9515,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3753" uniqueCount="498">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3779" uniqueCount="505">
   <si>
     <t>Verse Ref</t>
   </si>
@@ -11447,6 +11573,9 @@
     <t>Indpendent</t>
   </si>
   <si>
+    <t>% Dual:</t>
+  </si>
+  <si>
     <t>W/ Nons</t>
   </si>
   <si>
@@ -11721,6 +11850,24 @@
   </si>
   <si>
     <t>freq = κρατεω</t>
+  </si>
+  <si>
+    <t>Harmonization_Direction</t>
+  </si>
+  <si>
+    <t>Forward</t>
+  </si>
+  <si>
+    <t>Backward</t>
+  </si>
+  <si>
+    <t>Both</t>
+  </si>
+  <si>
+    <t>the phrase ουτω και occurs 6x more in the near context (cf. v. 2), always without the sigma; apograph disharmonizes</t>
+  </si>
+  <si>
+    <t>Directionality</t>
   </si>
 </sst>
 </file>
@@ -15816,7 +15963,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="1828800" y="41802050"/>
+              <a:off x="1828800" y="43091100"/>
               <a:ext cx="3962400" cy="2792730"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -16323,6 +16470,27 @@
   <threadedComment ref="D7" dT="2024-01-24T17:16:15.06" personId="{5D048A0C-9405-47F1-A020-6E53793B23CD}" id="{FEF04B0C-A8B3-467D-A075-DE68F3219A8F}">
     <text>The ratio of harmonizations to disharmonizations; = harmonizations / (harmonizations + disharmonizations)</text>
   </threadedComment>
+  <threadedComment ref="E11" dT="2026-03-26T18:54:36.97" personId="{5D048A0C-9405-47F1-A020-6E53793B23CD}" id="{2CF52AFD-CF13-43C6-AE65-1932FB2EB6D6}">
+    <text>All cases where influence from preceding material was possible.</text>
+  </threadedComment>
+  <threadedComment ref="F11" dT="2026-03-26T18:55:05.59" personId="{5D048A0C-9405-47F1-A020-6E53793B23CD}" id="{21F00353-2015-4D13-8645-46E303C433F1}">
+    <text>All cases where influence from following material was possible.</text>
+  </threadedComment>
+  <threadedComment ref="G11" dT="2026-03-26T18:56:11.72" personId="{5D048A0C-9405-47F1-A020-6E53793B23CD}" id="{D0F8D6BD-068D-4303-9C66-A12845C898DE}">
+    <text>Only cases where verbal parallels existed both behind and after the variant in question and the direction of change in verbal similarity was the same.</text>
+  </threadedComment>
+  <threadedComment ref="H11" dT="2026-03-26T18:56:36.44" personId="{5D048A0C-9405-47F1-A020-6E53793B23CD}" id="{91566328-4150-49AD-9102-B38078C2A212}">
+    <text>All potential cases of verbal harmonization/disharmonization, forward and backward.</text>
+  </threadedComment>
+  <threadedComment ref="D12" dT="2024-01-24T17:15:11.25" personId="{5D048A0C-9405-47F1-A020-6E53793B23CD}" id="{C119846B-5B2A-4856-9CFB-216AD7D71EBB}">
+    <text>The number of variants that harmonized to parallel phrases in the near context</text>
+  </threadedComment>
+  <threadedComment ref="D13" dT="2024-01-24T17:15:35.01" personId="{5D048A0C-9405-47F1-A020-6E53793B23CD}" id="{48C6D0FD-C6F8-45F8-B647-860ADD900CBF}">
+    <text>The number of variants that disharmonized from  parallel phrases in the near context</text>
+  </threadedComment>
+  <threadedComment ref="D14" dT="2024-01-24T17:16:15.06" personId="{5D048A0C-9405-47F1-A020-6E53793B23CD}" id="{0D18526A-8833-4BFE-A5AB-CA0051C886F9}">
+    <text>The ratio of harmonizations to disharmonizations; = harmonizations / (harmonizations + disharmonizations)</text>
+  </threadedComment>
 </ThreadedComments>
 </file>
 
@@ -16348,16 +16516,16 @@
 
 <file path=xl/threadedComments/threadedComment15.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="K3" dT="2023-08-03T13:34:30.53" personId="{5D048A0C-9405-47F1-A020-6E53793B23CD}" id="{3B3C42D7-D23A-4A13-961D-A51B33C4F812}">
+  <threadedComment ref="L3" dT="2023-08-03T13:34:30.53" personId="{5D048A0C-9405-47F1-A020-6E53793B23CD}" id="{3B3C42D7-D23A-4A13-961D-A51B33C4F812}">
     <text>The apograph reading is singular and the autograph reading is not. The singular readings method would detect this variant</text>
   </threadedComment>
-  <threadedComment ref="K4" dT="2023-08-03T13:33:28.57" personId="{5D048A0C-9405-47F1-A020-6E53793B23CD}" id="{33503B61-D396-4CB6-B78C-738CF807F495}">
+  <threadedComment ref="L4" dT="2023-08-03T13:33:28.57" personId="{5D048A0C-9405-47F1-A020-6E53793B23CD}" id="{33503B61-D396-4CB6-B78C-738CF807F495}">
     <text>That is, the autograph contains a singular reading and the apograph followed it</text>
   </threadedComment>
-  <threadedComment ref="K5" dT="2023-08-03T13:35:10.13" personId="{5D048A0C-9405-47F1-A020-6E53793B23CD}" id="{578F9A70-DB86-4124-99A3-FB5E8B3F24F9}">
+  <threadedComment ref="L5" dT="2023-08-03T13:35:10.13" personId="{5D048A0C-9405-47F1-A020-6E53793B23CD}" id="{578F9A70-DB86-4124-99A3-FB5E8B3F24F9}">
     <text>The apograph reading is not singular: other witnesses contain the same reading. These are real variants produced by the apograph scribe, but the singular readings method would not detect them</text>
   </threadedComment>
-  <threadedComment ref="M13" dT="2023-08-14T14:21:11.11" personId="{5D048A0C-9405-47F1-A020-6E53793B23CD}" id="{CA332D3B-255C-4BFE-A327-192CC1243DCB}">
+  <threadedComment ref="N13" dT="2023-08-14T14:21:11.11" personId="{5D048A0C-9405-47F1-A020-6E53793B23CD}" id="{CA332D3B-255C-4BFE-A327-192CC1243DCB}">
     <text>For words which have multiple common forms not impacting their inflection (e.g., ουκ-ουχ-ου, επι-επ-εφ)</text>
   </threadedComment>
 </ThreadedComments>
@@ -16675,6 +16843,27 @@
   <threadedComment ref="D7" dT="2024-01-24T17:16:15.06" personId="{5D048A0C-9405-47F1-A020-6E53793B23CD}" id="{0AD6D9F9-2F1D-44BE-A953-FBE9B8E07C12}">
     <text>The ratio of harmonizations to disharmonizations; = harmonizations / (harmonizations + disharmonizations)</text>
   </threadedComment>
+  <threadedComment ref="E11" dT="2026-03-26T18:54:36.97" personId="{5D048A0C-9405-47F1-A020-6E53793B23CD}" id="{ED08F7F9-1454-4A27-8E33-0D39A1CDAA02}">
+    <text>All cases where influence from preceding material was possible.</text>
+  </threadedComment>
+  <threadedComment ref="F11" dT="2026-03-26T18:55:05.59" personId="{5D048A0C-9405-47F1-A020-6E53793B23CD}" id="{0AF28895-093D-4DC8-A63F-A8A5D20CF2B3}">
+    <text>All cases where influence from following material was possible.</text>
+  </threadedComment>
+  <threadedComment ref="G11" dT="2026-03-26T18:56:11.72" personId="{5D048A0C-9405-47F1-A020-6E53793B23CD}" id="{3974ECD3-1AA7-4B3E-80B0-1A60B8E1FB87}">
+    <text>Only cases where verbal parallels existed both behind and after the variant in question and the direction of change in verbal similarity was the same.</text>
+  </threadedComment>
+  <threadedComment ref="H11" dT="2026-03-26T18:56:36.44" personId="{5D048A0C-9405-47F1-A020-6E53793B23CD}" id="{AD3C4D56-9A0A-4345-8005-6EA35E72C7A6}">
+    <text>All potential cases of verbal harmonization/disharmonization, forward and backward.</text>
+  </threadedComment>
+  <threadedComment ref="D12" dT="2024-01-24T17:15:11.25" personId="{5D048A0C-9405-47F1-A020-6E53793B23CD}" id="{97DB7EF9-2486-4788-9B63-6F2F6CB3C1B9}">
+    <text>The number of variants that harmonized to parallel phrases in the near context</text>
+  </threadedComment>
+  <threadedComment ref="D13" dT="2024-01-24T17:15:35.01" personId="{5D048A0C-9405-47F1-A020-6E53793B23CD}" id="{AC9053CF-3511-46F8-956C-335082D56E88}">
+    <text>The number of variants that disharmonized from  parallel phrases in the near context</text>
+  </threadedComment>
+  <threadedComment ref="D14" dT="2024-01-24T17:16:15.06" personId="{5D048A0C-9405-47F1-A020-6E53793B23CD}" id="{68D9F6CF-BCFD-4577-9BE7-71C6F178CB12}">
+    <text>The ratio of harmonizations to disharmonizations; = harmonizations / (harmonizations + disharmonizations)</text>
+  </threadedComment>
 </ThreadedComments>
 </file>
 
@@ -16831,7 +17020,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78D9498E-60FE-47CE-98CB-DF81F2BD960C}">
-  <dimension ref="A1:AL123"/>
+  <dimension ref="A1:AL128"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="10.81640625" customWidth="1"/>
@@ -16914,10 +17103,10 @@
         <v>364</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="W1" s="1" t="s">
         <v>367</v>
@@ -16964,7 +17153,7 @@
         <v>38</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>158</v>
@@ -17539,10 +17728,10 @@
         <v>326</v>
       </c>
       <c r="P15" s="7" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="Q15" s="8" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="S15" s="7">
         <v>4</v>
@@ -18988,7 +19177,7 @@
         <v/>
       </c>
       <c r="AB53" s="7" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AD53" s="7" t="s">
         <v>19</v>
@@ -19151,7 +19340,7 @@
         <v>49</v>
       </c>
       <c r="AC57" s="7" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AD57" s="7" t="s">
         <v>19</v>
@@ -19489,7 +19678,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:36" ht="29">
+    <row r="66" spans="1:36" ht="43.5">
       <c r="A66" t="s">
         <v>112</v>
       </c>
@@ -19746,7 +19935,7 @@
         <v/>
       </c>
       <c r="AC72" s="7" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AD72" s="7" t="s">
         <v>19</v>
@@ -20922,7 +21111,7 @@
         <v/>
       </c>
       <c r="AC103" s="7" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AD103" s="7" t="s">
         <v>19</v>
@@ -21116,7 +21305,7 @@
         <v>19</v>
       </c>
       <c r="I108" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="J108" s="7" t="s">
         <v>24</v>
@@ -21373,10 +21562,10 @@
         <v>404</v>
       </c>
       <c r="AK117" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AL117" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="118" spans="1:38">
@@ -21384,10 +21573,10 @@
     </row>
     <row r="119" spans="1:38">
       <c r="D119" s="3" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AJ119" t="s">
         <v>405</v>
@@ -21403,7 +21592,7 @@
     </row>
     <row r="120" spans="1:38">
       <c r="D120" s="3" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E120" s="3">
         <v>27</v>
@@ -21421,16 +21610,27 @@
       </c>
     </row>
     <row r="121" spans="1:38">
-      <c r="E121" s="3" t="s">
-        <v>411</v>
+      <c r="D121" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="E121" s="3">
+        <v>20</v>
+      </c>
+      <c r="AJ121" t="s">
+        <v>406</v>
+      </c>
+      <c r="AK121">
+        <f>AK120/(AK119+AK120)</f>
+        <v>0.70642201834862384</v>
+      </c>
+      <c r="AL121">
+        <f>AL120/(AL119+AL120)</f>
+        <v>0.70642201834862384</v>
       </c>
     </row>
     <row r="122" spans="1:38">
-      <c r="D122" s="3" t="s">
-        <v>408</v>
-      </c>
-      <c r="E122" s="3">
-        <v>24</v>
+      <c r="E122" s="3" t="s">
+        <v>412</v>
       </c>
     </row>
     <row r="123" spans="1:38">
@@ -21438,7 +21638,21 @@
         <v>409</v>
       </c>
       <c r="E123" s="3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="124" spans="1:38">
+      <c r="D124" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="E124" s="3">
         <v>20</v>
+      </c>
+    </row>
+    <row r="128" spans="1:38">
+      <c r="E128" s="3">
+        <f>COUNTIF(F:F, "Autograph transcript error, but still a variant") + COUNTIF(F:F, "Apograph transcript error, but still a variant") + COUNTIF(F:F, "Not a variant: autograph transcript error") + COUNTIF(F:F, "Not a variant: apograph transcript error")</f>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -21544,6 +21758,12 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="15">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{7301F58A-7842-47E1-A459-B74EC9D1D65F}">
+          <x14:formula1>
+            <xm:f>'Data Regularization'!$Q$2:$Q$4</xm:f>
+          </x14:formula1>
+          <xm:sqref>AG2:AI1048576</xm:sqref>
+        </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{F296372A-82D7-4C15-8DFD-7B6F0274E2CD}">
           <x14:formula1>
             <xm:f>'Data Regularization'!$D$2:$D$1048576</xm:f>
@@ -21570,49 +21790,49 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{E58C8269-85C1-4954-94AF-53AEB6BB3AF2}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$J$2:$J$1048576</xm:f>
+            <xm:f>'Data Regularization'!$K$2:$K$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>W2:W1048576 Y2:Y1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{1551F1B6-52BD-424E-BAE3-B6C43C345BE1}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$K$2:$K$1048576</xm:f>
+            <xm:f>'Data Regularization'!$L$2:$L$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>Z2:Z1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{A2A165D6-3E6F-4690-8799-A94019E3C6D5}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$L$2:$L$1048576</xm:f>
+            <xm:f>'Data Regularization'!$M$2:$M$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AA2:AA1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C2D49E17-5064-4A0C-91D6-C555B2458E2D}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$M$2:$M$1048576</xm:f>
+            <xm:f>'Data Regularization'!$N$2:$N$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AB2:AB1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C86CB294-184E-427F-AD99-9FE4540AAE92}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$N$2:$N$1048576</xm:f>
+            <xm:f>'Data Regularization'!$O$2:$O$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AD2:AD1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{E6D4003E-6DB7-4E6F-87F4-36990610CF3F}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$O$2:$O$1048576</xm:f>
+            <xm:f>'Data Regularization'!$P$2:$P$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AE2:AE1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B5AD62D9-B213-4CA5-A230-16E4ED092956}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$P$2:$P$1048576</xm:f>
+            <xm:f>'Data Regularization'!$Q$2:$Q$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AF2:AF1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{2E62E8AD-BAD3-4EB9-AFBF-45839D0B1E9E}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$C$2:$C$50</xm:f>
+            <xm:f>'Data Regularization'!$C$2:$C$29</xm:f>
           </x14:formula1>
           <xm:sqref>H2:H1048576</xm:sqref>
         </x14:dataValidation>
@@ -21628,12 +21848,6 @@
           </x14:formula1>
           <xm:sqref>G2:G1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{7301F58A-7842-47E1-A459-B74EC9D1D65F}">
-          <x14:formula1>
-            <xm:f>'Data Regularization'!$P$2:$P$4</xm:f>
-          </x14:formula1>
-          <xm:sqref>AG2:AI1048576</xm:sqref>
-        </x14:dataValidation>
       </x14:dataValidations>
     </ext>
   </extLst>
@@ -21695,16 +21909,16 @@
         <v>363</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="R1" s="1" t="s">
         <v>364</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="U1" s="1" t="s">
         <v>367</v>
@@ -21787,10 +22001,10 @@
       </c>
       <c r="R2" s="7"/>
       <c r="S2" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T2" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U2" s="7"/>
       <c r="V2" s="7"/>
@@ -21849,10 +22063,10 @@
       </c>
       <c r="R3" s="7"/>
       <c r="S3" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T3" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U3" s="7"/>
       <c r="V3" s="7"/>
@@ -21911,10 +22125,10 @@
       </c>
       <c r="R4" s="7"/>
       <c r="S4" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T4" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U4" s="7"/>
       <c r="V4" s="7"/>
@@ -21977,10 +22191,10 @@
       </c>
       <c r="R5" s="7"/>
       <c r="S5" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T5" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U5" s="7"/>
       <c r="V5" s="7"/>
@@ -22039,10 +22253,10 @@
       </c>
       <c r="R6" s="7"/>
       <c r="S6" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T6" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U6" s="7"/>
       <c r="V6" s="7"/>
@@ -22101,10 +22315,10 @@
       </c>
       <c r="R7" s="7"/>
       <c r="S7" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T7" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U7" s="7"/>
       <c r="V7" s="7"/>
@@ -22163,10 +22377,10 @@
       </c>
       <c r="R8" s="7"/>
       <c r="S8" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T8" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U8" s="7"/>
       <c r="V8" s="7"/>
@@ -22227,10 +22441,10 @@
       </c>
       <c r="R9" s="7"/>
       <c r="S9" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T9" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U9" s="7"/>
       <c r="V9" s="7"/>
@@ -22289,10 +22503,10 @@
       </c>
       <c r="R10" s="7"/>
       <c r="S10" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T10" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U10" s="7"/>
       <c r="V10" s="7"/>
@@ -22314,7 +22528,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:34" ht="58">
+    <row r="11" spans="1:34" ht="72.5">
       <c r="A11" t="s">
         <v>89</v>
       </c>
@@ -22351,10 +22565,10 @@
       </c>
       <c r="R11" s="7"/>
       <c r="S11" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T11" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U11" s="7"/>
       <c r="V11" s="7"/>
@@ -22413,10 +22627,10 @@
       </c>
       <c r="R12" s="7"/>
       <c r="S12" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T12" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U12" s="7"/>
       <c r="V12" s="7"/>
@@ -22475,10 +22689,10 @@
       </c>
       <c r="R13" s="7"/>
       <c r="S13" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T13" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U13" s="7"/>
       <c r="V13" s="7"/>
@@ -22537,10 +22751,10 @@
       </c>
       <c r="R14" s="7"/>
       <c r="S14" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T14" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U14" s="7"/>
       <c r="V14" s="7"/>
@@ -22599,10 +22813,10 @@
       </c>
       <c r="R15" s="7"/>
       <c r="S15" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T15" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U15" s="7"/>
       <c r="V15" s="7"/>
@@ -22626,7 +22840,7 @@
     </row>
     <row r="18" spans="4:6">
       <c r="D18" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="E18">
         <v>20338</v>
@@ -22634,7 +22848,7 @@
     </row>
     <row r="19" spans="4:6">
       <c r="D19" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E19">
         <f>MEDIAN(Q:Q)</f>
@@ -22643,19 +22857,19 @@
     </row>
     <row r="22" spans="4:6">
       <c r="D22" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E22">
         <f>COUNTIFS(G:G, "Addition", Q:Q, "&gt;=" &amp; $E$19)</f>
         <v>4</v>
       </c>
       <c r="F22" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="23" spans="4:6">
       <c r="D23" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="E23">
         <f>COUNTIFS(G:G, "Omission", Q:Q, "&gt;=" &amp; $E$19)</f>
@@ -22664,7 +22878,7 @@
     </row>
     <row r="24" spans="4:6">
       <c r="D24" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E24">
         <f>E22/(E22+E23)</f>
@@ -22673,7 +22887,7 @@
     </row>
     <row r="25" spans="4:6">
       <c r="D25" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E25">
         <f>COUNTIFS(G:G, "Addition", Q:Q, "&lt;" &amp; $E$19)</f>
@@ -22682,7 +22896,7 @@
     </row>
     <row r="26" spans="4:6">
       <c r="D26" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E26">
         <f>COUNTIFS(G:G, "Omission", Q:Q, "&lt;" &amp; $E$19)</f>
@@ -22691,7 +22905,7 @@
     </row>
     <row r="27" spans="4:6">
       <c r="D27" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E27">
         <f>E25/(E25+E26)</f>
@@ -22700,7 +22914,7 @@
     </row>
     <row r="30" spans="4:6">
       <c r="D30" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E30">
         <f>COUNTIFS(G:G, "Addition", K:K, "Article")</f>
@@ -22709,7 +22923,7 @@
     </row>
     <row r="31" spans="4:6">
       <c r="D31" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="E31">
         <f>COUNTIFS(G:G, "Omission", K:K, "Article")</f>
@@ -22718,7 +22932,7 @@
     </row>
     <row r="32" spans="4:6">
       <c r="D32" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E32">
         <f>COUNTIFS(G:G, "Addition", K:K, "Article")/(COUNTIFS(G:G, "Addition", K:K, "Article") + COUNTIFS(G:G, "Omission", K:K, "Article"))</f>
@@ -22839,6 +23053,12 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="15">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{3EC4AD85-A22F-409B-94F6-D984B50F09A2}">
+          <x14:formula1>
+            <xm:f>'Data Regularization'!$Q$2:$Q$4</xm:f>
+          </x14:formula1>
+          <xm:sqref>AG2:AG15 AE2:AE15</xm:sqref>
+        </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{87FE700C-6471-42B1-99FD-C0335A2C7959}">
           <x14:formula1>
             <xm:f>'Data Regularization'!$D$2:$D$1048576</xm:f>
@@ -22865,49 +23085,49 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{1D83ACD6-4F78-4440-8A3C-9F40F7DCED1C}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$J$2:$J$1048576</xm:f>
+            <xm:f>'Data Regularization'!$K$2:$K$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>U2:U15 W2:W15</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{A573537C-D222-4BFE-821A-3DD1318F084A}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$K$2:$K$1048576</xm:f>
+            <xm:f>'Data Regularization'!$L$2:$L$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>X2:X15</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{01399F67-3716-49DB-A265-52D1CF1A9B5E}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$L$2:$L$1048576</xm:f>
+            <xm:f>'Data Regularization'!$M$2:$M$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>Y2:Y15</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{E975D31D-077C-48B1-99B4-C372ABA57CCC}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$M$2:$M$1048576</xm:f>
+            <xm:f>'Data Regularization'!$N$2:$N$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>Z2:Z15</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{1A5820D5-094C-4B45-BA97-05A15FC6F78B}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$N$2:$N$1048576</xm:f>
+            <xm:f>'Data Regularization'!$O$2:$O$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AB2:AB15</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D93E98DF-831D-47D9-9B2F-5F0F2811C3D4}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$O$2:$O$1048576</xm:f>
+            <xm:f>'Data Regularization'!$P$2:$P$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AC2:AC15</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C3F52DAB-E4EF-4148-8631-1A59BEBB2DDB}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$P$2:$P$1048576</xm:f>
+            <xm:f>'Data Regularization'!$Q$2:$Q$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AD2:AD15</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{F912E4D4-9ACB-4C47-8B0E-AC827DB2D8AF}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$C$2:$C$50</xm:f>
+            <xm:f>'Data Regularization'!$C$2:$C$29</xm:f>
           </x14:formula1>
           <xm:sqref>F2:F15</xm:sqref>
         </x14:dataValidation>
@@ -22923,12 +23143,6 @@
           </x14:formula1>
           <xm:sqref>E2:E15</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{3EC4AD85-A22F-409B-94F6-D984B50F09A2}">
-          <x14:formula1>
-            <xm:f>'Data Regularization'!$P$2:$P$4</xm:f>
-          </x14:formula1>
-          <xm:sqref>AG2:AG15 AE2:AE15</xm:sqref>
-        </x14:dataValidation>
       </x14:dataValidations>
     </ext>
   </extLst>
@@ -22990,16 +23204,16 @@
         <v>363</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="R1" s="1" t="s">
         <v>364</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="U1" s="1" t="s">
         <v>367</v>
@@ -23071,10 +23285,10 @@
         <v>326</v>
       </c>
       <c r="M2" s="7" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="N2" s="8" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="O2" s="7"/>
       <c r="P2" s="7">
@@ -23085,10 +23299,10 @@
       </c>
       <c r="R2" s="7"/>
       <c r="S2" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T2" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U2" s="7"/>
       <c r="V2" s="7"/>
@@ -23147,10 +23361,10 @@
       </c>
       <c r="R3" s="7"/>
       <c r="S3" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T3" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U3" s="7"/>
       <c r="V3" s="7"/>
@@ -23174,7 +23388,7 @@
     </row>
     <row r="6" spans="1:34">
       <c r="D6" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="E6">
         <v>20338</v>
@@ -23182,7 +23396,7 @@
     </row>
     <row r="7" spans="1:34">
       <c r="D7" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E7">
         <f>MEDIAN(Q:Q)</f>
@@ -23191,19 +23405,19 @@
     </row>
     <row r="10" spans="1:34">
       <c r="D10" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E10">
         <f>COUNTIFS(G:G, "Addition", Q:Q, "&gt;=" &amp; $E$7)</f>
         <v>0</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="11" spans="1:34">
       <c r="D11" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="E11">
         <f>COUNTIFS(G:G, "Omission", Q:Q, "&gt;=" &amp; $E$7)</f>
@@ -23212,7 +23426,7 @@
     </row>
     <row r="12" spans="1:34">
       <c r="D12" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E12">
         <f>E10/(E10+E11)</f>
@@ -23221,7 +23435,7 @@
     </row>
     <row r="13" spans="1:34">
       <c r="D13" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E13">
         <f>COUNTIFS(G:G, "Addition", Q:Q, "&lt;" &amp; $E$7)</f>
@@ -23230,7 +23444,7 @@
     </row>
     <row r="14" spans="1:34">
       <c r="D14" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E14">
         <f>COUNTIFS(G:G, "Omission", Q:Q, "&lt;" &amp; $E$7)</f>
@@ -23239,7 +23453,7 @@
     </row>
     <row r="15" spans="1:34">
       <c r="D15" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E15">
         <f>E13/(E13+E14)</f>
@@ -23248,7 +23462,7 @@
     </row>
     <row r="16" spans="1:34">
       <c r="D16" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E16">
         <f>E12-E15</f>
@@ -23368,6 +23582,12 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="15">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{13E6DA6B-F2A3-414A-9744-CBE61016E137}">
+          <x14:formula1>
+            <xm:f>'Data Regularization'!$Q$2:$Q$4</xm:f>
+          </x14:formula1>
+          <xm:sqref>AG2:AG3 AE2:AE3</xm:sqref>
+        </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{A5BF6DA9-A46A-4225-8087-30EB7C348908}">
           <x14:formula1>
             <xm:f>'Data Regularization'!$D$2:$D$1048576</xm:f>
@@ -23394,49 +23614,49 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{241A5A7B-E2C3-450F-8200-B7EF86F06A09}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$J$2:$J$1048576</xm:f>
+            <xm:f>'Data Regularization'!$K$2:$K$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>W2:W3 U2:U3</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{9E17ECE3-D650-406C-9B9E-794C7351B431}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$K$2:$K$1048576</xm:f>
+            <xm:f>'Data Regularization'!$L$2:$L$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>X2:X3</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{822460C6-31C8-48FD-B0AC-3263EDC2F6AF}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$L$2:$L$1048576</xm:f>
+            <xm:f>'Data Regularization'!$M$2:$M$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>Y2:Y3</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B4E6C077-162C-4431-97A0-B8BD3756FA35}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$M$2:$M$1048576</xm:f>
+            <xm:f>'Data Regularization'!$N$2:$N$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>Z2:Z3</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C306323E-28B9-4A5C-B5BC-C668C0233D93}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$N$2:$N$1048576</xm:f>
+            <xm:f>'Data Regularization'!$O$2:$O$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AB2:AB3</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{AF82709D-0FF5-4C02-BBD8-70CD10E950EC}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$O$2:$O$1048576</xm:f>
+            <xm:f>'Data Regularization'!$P$2:$P$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AC2:AC3</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{ABB119E6-7CE5-45AA-B77D-845038E75282}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$P$2:$P$1048576</xm:f>
+            <xm:f>'Data Regularization'!$Q$2:$Q$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AD2:AD3</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{7DE4B289-756E-4F65-981A-68755677DEC5}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$C$2:$C$50</xm:f>
+            <xm:f>'Data Regularization'!$C$2:$C$29</xm:f>
           </x14:formula1>
           <xm:sqref>F2:F3</xm:sqref>
         </x14:dataValidation>
@@ -23452,12 +23672,6 @@
           </x14:formula1>
           <xm:sqref>E2:E3</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{13E6DA6B-F2A3-414A-9744-CBE61016E137}">
-          <x14:formula1>
-            <xm:f>'Data Regularization'!$P$2:$P$4</xm:f>
-          </x14:formula1>
-          <xm:sqref>AG2:AG3 AE2:AE3</xm:sqref>
-        </x14:dataValidation>
       </x14:dataValidations>
     </ext>
   </extLst>
@@ -23522,19 +23736,19 @@
         <v>364</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="W1" s="1" t="s">
         <v>367</v>
@@ -23761,7 +23975,7 @@
     </row>
     <row r="7" spans="1:36">
       <c r="D7" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="E7">
         <v>20338</v>
@@ -23769,7 +23983,7 @@
     </row>
     <row r="10" spans="1:36">
       <c r="D10" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E10">
         <f>COUNTIF(Q:Q, "&gt;0")</f>
@@ -23778,7 +23992,7 @@
     </row>
     <row r="11" spans="1:36">
       <c r="D11" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E11">
         <f>COUNTIF(Q:Q, "&lt;0")</f>
@@ -23787,7 +24001,7 @@
     </row>
     <row r="12" spans="1:36">
       <c r="D12" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E12">
         <f>_xlfn.BINOM.DIST(MIN(E10,E11),(E10+E11),0.5,TRUE)*2</f>
@@ -23796,7 +24010,7 @@
     </row>
     <row r="14" spans="1:36">
       <c r="D14" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E14">
         <f>AVERAGE(Q:Q)</f>
@@ -23805,7 +24019,7 @@
     </row>
     <row r="15" spans="1:36">
       <c r="D15" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="E15">
         <f>_xlfn.STDEV.S(Q:Q)</f>
@@ -23814,7 +24028,7 @@
     </row>
     <row r="18" spans="4:5">
       <c r="D18" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="E18">
         <f>AVERAGE(V:V)</f>
@@ -23823,7 +24037,7 @@
     </row>
     <row r="19" spans="4:5">
       <c r="D19" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="E19">
         <f>_xlfn.STDEV.S(V:V)</f>
@@ -23832,7 +24046,7 @@
     </row>
     <row r="22" spans="4:5">
       <c r="D22" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E22">
         <f>COUNT(V:V)</f>
@@ -23841,7 +24055,7 @@
     </row>
     <row r="23" spans="4:5">
       <c r="D23" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E23">
         <f>_xlfn.STDEV.P(V:V)</f>
@@ -23951,6 +24165,12 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="15">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{071A6C03-AB9E-4CF5-A533-29B0B053102B}">
+          <x14:formula1>
+            <xm:f>'Data Regularization'!$Q$2:$Q$4</xm:f>
+          </x14:formula1>
+          <xm:sqref>AI2:AI4 AG2:AG4</xm:sqref>
+        </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{1BE4DC1D-AEFE-4E1F-9876-B22F6E4A7D4F}">
           <x14:formula1>
             <xm:f>'Data Regularization'!$D$2:$D$1048576</xm:f>
@@ -23977,49 +24197,49 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{36ED0C3E-32A4-4A5E-9BE6-15D00D8BAEB4}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$J$2:$J$1048576</xm:f>
+            <xm:f>'Data Regularization'!$K$2:$K$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>Y2:Y4 W2:W4</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B5063263-6EA6-4173-8D3E-AF23FA1CA10B}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$K$2:$K$1048576</xm:f>
+            <xm:f>'Data Regularization'!$L$2:$L$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>Z2:Z4</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{73450556-44A8-46B8-8168-20F0EC4CF16D}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$L$2:$L$1048576</xm:f>
+            <xm:f>'Data Regularization'!$M$2:$M$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AA2:AA4</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{62FE57C8-0422-410A-A482-F3E9E7EA0C63}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$M$2:$M$1048576</xm:f>
+            <xm:f>'Data Regularization'!$N$2:$N$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AB2:AB4</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C2985FC6-BE34-43CB-B749-8B1761A9E3ED}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$N$2:$N$1048576</xm:f>
+            <xm:f>'Data Regularization'!$O$2:$O$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AD2:AD4</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{4AE05664-F17D-4845-B595-448F445BFF39}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$O$2:$O$1048576</xm:f>
+            <xm:f>'Data Regularization'!$P$2:$P$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AE2:AE4</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{6F52AB43-E615-476C-804E-684478651CE4}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$P$2:$P$1048576</xm:f>
+            <xm:f>'Data Regularization'!$Q$2:$Q$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AF2:AF4</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{EB325734-5977-4830-BCBD-DBF5E9239624}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$C$2:$C$50</xm:f>
+            <xm:f>'Data Regularization'!$C$2:$C$29</xm:f>
           </x14:formula1>
           <xm:sqref>F2:F4</xm:sqref>
         </x14:dataValidation>
@@ -24035,12 +24255,6 @@
           </x14:formula1>
           <xm:sqref>E2:E4</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{071A6C03-AB9E-4CF5-A533-29B0B053102B}">
-          <x14:formula1>
-            <xm:f>'Data Regularization'!$P$2:$P$4</xm:f>
-          </x14:formula1>
-          <xm:sqref>AI2:AI4 AG2:AG4</xm:sqref>
-        </x14:dataValidation>
       </x14:dataValidations>
     </ext>
   </extLst>
@@ -24049,10 +24263,10 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E925D12-6B7D-4385-A278-3A874E564833}">
-  <dimension ref="A1:AH7"/>
+  <dimension ref="A1:AI14"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
-    <row r="1" spans="1:34" s="1" customFormat="1" ht="29">
+    <row r="1" spans="1:35" s="1" customFormat="1" ht="29">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -24108,52 +24322,55 @@
         <v>364</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="U1" s="1" t="s">
         <v>367</v>
       </c>
       <c r="V1" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="W1" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="2" spans="1:34" ht="29">
+    <row r="2" spans="1:35" ht="29">
       <c r="A2" t="s">
         <v>120</v>
       </c>
@@ -24164,7 +24381,7 @@
         <v>189</v>
       </c>
       <c r="G2" t="s">
-        <v>401</v>
+        <v>503</v>
       </c>
       <c r="H2" s="7" t="s">
         <v>374</v>
@@ -24180,15 +24397,17 @@
       <c r="Q2" s="7"/>
       <c r="R2" s="7"/>
       <c r="S2" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T2" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U2" s="7" t="s">
         <v>371</v>
       </c>
-      <c r="V2" s="7"/>
+      <c r="V2" s="7" t="s">
+        <v>502</v>
+      </c>
       <c r="W2" s="7"/>
       <c r="X2" s="7"/>
       <c r="Y2" s="7"/>
@@ -24197,44 +24416,133 @@
       <c r="AB2" s="7"/>
       <c r="AC2" s="7"/>
       <c r="AD2" s="7"/>
-      <c r="AE2" t="s">
-        <v>19</v>
-      </c>
+      <c r="AE2" s="7"/>
       <c r="AF2" t="s">
+        <v>19</v>
+      </c>
+      <c r="AG2" t="s">
         <v>20</v>
       </c>
-      <c r="AH2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:34">
+      <c r="AI2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:35">
       <c r="D5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="E5">
         <f>COUNTIF(U:U, "Harmonizing")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34">
+    <row r="6" spans="1:35">
       <c r="D6" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="E6">
         <f>COUNTIF(U:U, "Disharmonizing")</f>
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34">
+    <row r="7" spans="1:35">
       <c r="D7" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E7">
         <f>E5/(E5+E6)</f>
         <v>0</v>
       </c>
     </row>
+    <row r="10" spans="1:35">
+      <c r="E10" s="11" t="s">
+        <v>504</v>
+      </c>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+    </row>
+    <row r="11" spans="1:35">
+      <c r="E11" t="s">
+        <v>500</v>
+      </c>
+      <c r="F11" t="s">
+        <v>501</v>
+      </c>
+      <c r="G11" t="s">
+        <v>502</v>
+      </c>
+      <c r="H11" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="12" spans="1:35">
+      <c r="D12" t="s">
+        <v>479</v>
+      </c>
+      <c r="E12">
+        <f>COUNTIFS($U$2:$U$2,"Harmonizing",$V$2:$V$2,"forward") + COUNTIFS($U$2:$U$2,"Harmonizing",$V$2:$V$2,"both")</f>
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <f>COUNTIFS($U$2:$U$2,"Harmonizing",$V$2:$V$2,"backward") + COUNTIFS($U$2:$U$2,"Harmonizing",$V$2:$V$2,"both")</f>
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <f>COUNTIFS($U$2:$U$2,"Harmonizing",$V$2:$V$2,"both")</f>
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <f>COUNTIFS($U$2:$U$2,"Harmonizing",$V$2:$V$2,"both") + COUNTIFS($U$2:$U$2,"Harmonizing",$V$2:$V$2,"forward") + COUNTIFS($U$2:$U$2,"Harmonizing",$V$2:$V$2,"backward")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35">
+      <c r="D13" t="s">
+        <v>480</v>
+      </c>
+      <c r="E13">
+        <f>COUNTIFS($U$2:$U$2,"Disharmonizing",$V$2:$V$2,"forward") + COUNTIFS($U$2:$U$2,"Disharmonizing",$V$2:$V$2,"both")</f>
+        <v>1</v>
+      </c>
+      <c r="F13">
+        <f>COUNTIFS($U$2:$U$2,"Disharmonizing",$V$2:$V$2,"backward") + COUNTIFS($U$2:$U$2,"Disharmonizing",$V$2:$V$2,"both")</f>
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <f>COUNTIFS($U$2:$U$2,"Disharmonizing",$V$2:$V$2,"both")</f>
+        <v>1</v>
+      </c>
+      <c r="H13">
+        <f>COUNTIFS($U$2:$U$2,"Disharmonizing",$V$2:$V$2,"both") + COUNTIFS($U$2:$U$2,"Disharmonizing",$V$2:$V$2,"forward") + COUNTIFS($U$2:$U$2,"Disharmonizing",$V$2:$V$2,"backward")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35">
+      <c r="D14" t="s">
+        <v>481</v>
+      </c>
+      <c r="E14">
+        <f>E12/(E12+E13)</f>
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <f t="shared" ref="F14:H14" si="0">F12/(F12+F13)</f>
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="E10:H10"/>
+  </mergeCells>
   <conditionalFormatting sqref="H2">
     <cfRule type="expression" dxfId="25" priority="4">
       <formula>$J2&lt;&gt;""</formula>
@@ -24282,10 +24590,10 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="R2">
     <cfRule type="expression" dxfId="14" priority="17">
-      <formula>AND(AND(LEFT($J2,3)="Sub", RIGHT($J2,4)&lt;&gt;"Form"),$V2&lt;&gt;"")</formula>
+      <formula>AND(AND(LEFT($J2,3)="Sub", RIGHT($J2,4)&lt;&gt;"Form"),$W2&lt;&gt;"")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="13" priority="18">
-      <formula>AND(AND(LEFT($J2,3)="Sub", RIGHT($J2,4)&lt;&gt;"Form"),$V2="")</formula>
+      <formula>AND(AND(LEFT($J2,3)="Sub", RIGHT($J2,4)&lt;&gt;"Form"),$W2="")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="12" priority="19">
       <formula>"&lt;&gt;AND(LEFT($J2,3)=""Sub"", RIGHT($J2,4)&lt;&gt;""Form"")"</formula>
@@ -24302,18 +24610,18 @@
       <formula>"&lt;&gt;AND(LEFT($J2,3)=""Sub"", RIGHT($J2,4)&lt;&gt;""Form"")"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U2">
+  <conditionalFormatting sqref="U2:V2">
     <cfRule type="expression" dxfId="8" priority="7">
-      <formula>AND($W2&lt;&gt;"",OR($AD2="Yes",$AE2&lt;&gt;""))</formula>
+      <formula>AND($X2&lt;&gt;"",OR($AE2="Yes",$AF2&lt;&gt;""))</formula>
     </cfRule>
     <cfRule type="expression" dxfId="7" priority="8">
-      <formula>OR($AD2="Yes",$AE2&lt;&gt;"")</formula>
+      <formula>OR($AE2="Yes",$AF2&lt;&gt;"")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="6" priority="25">
-      <formula>AND($AD2&lt;&gt;"Yes",$AE2="")</formula>
+      <formula>AND($AE2&lt;&gt;"Yes",$AF2="")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U2:AD2">
+  <conditionalFormatting sqref="U2:AE2">
     <cfRule type="expression" dxfId="5" priority="23">
       <formula>AND($J2&lt;&gt;"",$J2&lt;&gt;"Unclear due to correction")</formula>
     </cfRule>
@@ -24321,32 +24629,44 @@
       <formula>OR($J2="",$J2="Unclear due to correction")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V2">
+  <conditionalFormatting sqref="W2">
     <cfRule type="expression" dxfId="3" priority="6">
-      <formula>AND($J2&lt;&gt;"",$J2&lt;&gt;"Unclear due to correction",$X2="")</formula>
+      <formula>AND($J2&lt;&gt;"",$J2&lt;&gt;"Unclear due to correction",$Y2="")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="W2">
+  <conditionalFormatting sqref="X2">
     <cfRule type="expression" dxfId="2" priority="9">
-      <formula>AND($X2="Yes",$Y2="")</formula>
+      <formula>AND($Y2="Yes",$Z2="")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="1" priority="10">
-      <formula>$X2=""</formula>
+      <formula>$Y2=""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AB2">
+  <conditionalFormatting sqref="AC2">
     <cfRule type="expression" dxfId="0" priority="26">
-      <formula>AND(OR($AB2&lt;&gt;"",$AC2&lt;&gt;""),$AD2="")</formula>
+      <formula>AND(OR($AC2&lt;&gt;"",$AD2&lt;&gt;""),$AE2="")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showInputMessage="1" sqref="V2" xr:uid="{2B41D06C-E6B1-4F2C-9DA9-795A254EC929}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" sqref="W2" xr:uid="{2B41D06C-E6B1-4F2C-9DA9-795A254EC929}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="15">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="16">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{509D3B6E-6353-41F9-B447-D15DCB8A4563}">
+          <x14:formula1>
+            <xm:f>'Data Regularization'!$Q$2:$Q$4</xm:f>
+          </x14:formula1>
+          <xm:sqref>AF2:AH2</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{92FAB266-3E26-42A5-99B0-DEA974FB9DE8}">
+          <x14:formula1>
+            <xm:f>'Data Regularization'!$I$2:$I$5</xm:f>
+          </x14:formula1>
+          <xm:sqref>V2</xm:sqref>
+        </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{6150797D-4F67-42EE-8B1C-836002A9BEB0}">
           <x14:formula1>
             <xm:f>'Data Regularization'!$D$2:$D$1048576</xm:f>
@@ -24373,49 +24693,49 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{17DC3ABB-4EFB-4220-8A21-B970FBD87280}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$J$2:$J$1048576</xm:f>
+            <xm:f>'Data Regularization'!$K$2:$K$1048576</xm:f>
           </x14:formula1>
-          <xm:sqref>W2 U2</xm:sqref>
+          <xm:sqref>X2 U2</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{0611C09F-51D8-4D9E-8D71-098D8F432781}">
-          <x14:formula1>
-            <xm:f>'Data Regularization'!$K$2:$K$1048576</xm:f>
-          </x14:formula1>
-          <xm:sqref>X2</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D57CE7F7-2DE1-4D31-9D7A-32A88B3015C5}">
           <x14:formula1>
             <xm:f>'Data Regularization'!$L$2:$L$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>Y2</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{4A0966E9-3A11-4CB1-B860-8B8063FCB08C}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D57CE7F7-2DE1-4D31-9D7A-32A88B3015C5}">
           <x14:formula1>
             <xm:f>'Data Regularization'!$M$2:$M$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>Z2</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B3CDB78D-7485-42A1-B6FF-D0490DE9D03D}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{4A0966E9-3A11-4CB1-B860-8B8063FCB08C}">
           <x14:formula1>
             <xm:f>'Data Regularization'!$N$2:$N$1048576</xm:f>
           </x14:formula1>
-          <xm:sqref>AB2</xm:sqref>
+          <xm:sqref>AA2</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{25C423CA-C589-4E20-B43F-B63AB8FF1171}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B3CDB78D-7485-42A1-B6FF-D0490DE9D03D}">
           <x14:formula1>
             <xm:f>'Data Regularization'!$O$2:$O$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AC2</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{83345875-A76E-4F1F-B44F-D11F7DEB2147}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{25C423CA-C589-4E20-B43F-B63AB8FF1171}">
           <x14:formula1>
             <xm:f>'Data Regularization'!$P$2:$P$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AD2</xm:sqref>
         </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{83345875-A76E-4F1F-B44F-D11F7DEB2147}">
+          <x14:formula1>
+            <xm:f>'Data Regularization'!$Q$2:$Q$1048576</xm:f>
+          </x14:formula1>
+          <xm:sqref>AE2</xm:sqref>
+        </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{6950A105-9CA1-4662-BD7D-A93261DEF709}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$C$2:$C$50</xm:f>
+            <xm:f>'Data Regularization'!$C$2:$C$29</xm:f>
           </x14:formula1>
           <xm:sqref>F2</xm:sqref>
         </x14:dataValidation>
@@ -24430,12 +24750,6 @@
             <xm:f>'Data Regularization'!$B$2:$B$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>E2</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{509D3B6E-6353-41F9-B447-D15DCB8A4563}">
-          <x14:formula1>
-            <xm:f>'Data Regularization'!$P$2:$P$4</xm:f>
-          </x14:formula1>
-          <xm:sqref>AE2:AG2</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -24453,7 +24767,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B1">
         <v>1711</v>
@@ -24461,7 +24775,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B2">
         <f>COUNTA('Unfiltered Data'!A:A) - 1</f>
@@ -24470,7 +24784,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B3">
         <f>COUNTA('Gen-filters'!A:A) - 1</f>
@@ -24479,7 +24793,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B5">
         <f>(B2/B1)*1000</f>
@@ -24488,7 +24802,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B6">
         <f>(B3/B1)*1000</f>
@@ -24509,7 +24823,7 @@
   <sheetData>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -24532,7 +24846,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B5">
         <f>B3/SUM(B3:B4)</f>
@@ -24541,18 +24855,18 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="B9" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C9" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D9" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -24574,7 +24888,7 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B11">
         <f>COUNTIF('Unfiltered Data'!H:H, "Yes, partially")</f>
@@ -24591,7 +24905,7 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B12">
         <f>COUNTIF('Unfiltered Data'!H:H, "Yes, to another error")</f>
@@ -24613,10 +24927,10 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70C156D7-421F-42E5-9F55-F22A94A76A4F}">
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -24642,34 +24956,37 @@
         <v>367</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:17">
       <c r="A2" s="1"/>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:17">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -24695,31 +25012,34 @@
         <v>4</v>
       </c>
       <c r="I3" t="s">
-        <v>19</v>
+        <v>500</v>
       </c>
       <c r="J3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K3" t="s">
         <v>4</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>328</v>
       </c>
-      <c r="L3" t="s">
-        <v>19</v>
-      </c>
       <c r="M3" t="s">
+        <v>19</v>
+      </c>
+      <c r="N3" t="s">
         <v>329</v>
       </c>
-      <c r="N3" t="s">
-        <v>19</v>
-      </c>
       <c r="O3" t="s">
+        <v>19</v>
+      </c>
+      <c r="P3" t="s">
         <v>330</v>
       </c>
-      <c r="P3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16">
+      <c r="Q3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -24745,31 +25065,34 @@
         <v>371</v>
       </c>
       <c r="I4" t="s">
+        <v>501</v>
+      </c>
+      <c r="J4" t="s">
         <v>20</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>371</v>
       </c>
-      <c r="K4" t="s">
-        <v>486</v>
-      </c>
       <c r="L4" t="s">
+        <v>487</v>
+      </c>
+      <c r="M4" t="s">
         <v>20</v>
       </c>
-      <c r="M4" t="s">
+      <c r="N4" t="s">
         <v>335</v>
       </c>
-      <c r="N4" t="s">
+      <c r="O4" t="s">
         <v>20</v>
       </c>
-      <c r="O4" t="s">
+      <c r="P4" t="s">
         <v>336</v>
       </c>
-      <c r="P4" t="s">
+      <c r="Q4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:17">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -24788,17 +25111,20 @@
       <c r="F5" t="s">
         <v>373</v>
       </c>
-      <c r="K5" t="s">
+      <c r="I5" t="s">
+        <v>502</v>
+      </c>
+      <c r="L5" t="s">
         <v>334</v>
       </c>
-      <c r="M5" t="s">
+      <c r="N5" t="s">
         <v>339</v>
       </c>
-      <c r="O5" t="s">
+      <c r="P5" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:17">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -24811,14 +25137,14 @@
       <c r="E6" t="s">
         <v>341</v>
       </c>
-      <c r="M6" t="s">
+      <c r="N6" t="s">
         <v>342</v>
       </c>
-      <c r="O6" t="s">
+      <c r="P6" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="7" spans="1:16">
+    <row r="7" spans="1:17">
       <c r="A7" t="s">
         <v>28</v>
       </c>
@@ -24828,11 +25154,11 @@
       <c r="E7" t="s">
         <v>344</v>
       </c>
-      <c r="M7" t="s">
+      <c r="N7" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="8" spans="1:16">
+    <row r="8" spans="1:17">
       <c r="A8" t="s">
         <v>29</v>
       </c>
@@ -24842,11 +25168,11 @@
       <c r="E8" t="s">
         <v>346</v>
       </c>
-      <c r="M8" t="s">
+      <c r="N8" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="9" spans="1:16">
+    <row r="9" spans="1:17">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -24856,11 +25182,11 @@
       <c r="E9" t="s">
         <v>348</v>
       </c>
-      <c r="M9" t="s">
+      <c r="N9" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="10" spans="1:16">
+    <row r="10" spans="1:17">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -24870,44 +25196,44 @@
       <c r="E10" t="s">
         <v>350</v>
       </c>
-      <c r="M10" t="s">
+      <c r="N10" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="11" spans="1:16">
+    <row r="11" spans="1:17">
       <c r="A11" t="s">
         <v>18</v>
       </c>
       <c r="E11" t="s">
         <v>352</v>
       </c>
-      <c r="M11" t="s">
+      <c r="N11" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="12" spans="1:16">
+    <row r="12" spans="1:17">
       <c r="A12" t="s">
         <v>376</v>
       </c>
       <c r="E12" t="s">
         <v>377</v>
       </c>
-      <c r="M12" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16">
+      <c r="N12" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17">
       <c r="A13" t="s">
         <v>31</v>
       </c>
       <c r="E13" t="s">
         <v>383</v>
       </c>
-      <c r="M13" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16">
+      <c r="N13" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17">
       <c r="A14" t="s">
         <v>32</v>
       </c>
@@ -24915,12 +25241,12 @@
         <v>353</v>
       </c>
     </row>
-    <row r="15" spans="1:16">
+    <row r="15" spans="1:17">
       <c r="A15" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="16" spans="1:16">
+    <row r="16" spans="1:17">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -24942,7 +25268,7 @@
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="21" spans="1:1">
@@ -24958,13 +25284,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A51AA501-5C31-4DF1-B0EE-7C895471879E}">
-  <dimension ref="A1:AG87"/>
+  <dimension ref="A1:AG84"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="10.453125" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="20.81640625" customWidth="1"/>
-    <col min="4" max="6" width="8.90625" hidden="1" customWidth="1"/>
-    <col min="7" max="30" width="8.90625" customWidth="1"/>
+    <col min="4" max="30" width="8.90625" customWidth="1"/>
     <col min="34" max="34" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -25021,10 +25346,10 @@
         <v>364</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="T1" s="1" t="s">
         <v>367</v>
@@ -25071,7 +25396,7 @@
         <v>38</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>158</v>
@@ -25100,10 +25425,10 @@
       </c>
       <c r="Q2" s="7"/>
       <c r="R2" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S2" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T2" s="7"/>
       <c r="U2" s="7"/>
@@ -25163,10 +25488,10 @@
       </c>
       <c r="Q3" s="7"/>
       <c r="R3" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S3" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T3" s="7"/>
       <c r="U3" s="7"/>
@@ -25222,10 +25547,10 @@
       </c>
       <c r="Q4" s="7"/>
       <c r="R4" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S4" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T4" s="7"/>
       <c r="U4" s="7"/>
@@ -25271,10 +25596,10 @@
       <c r="P5" s="7"/>
       <c r="Q5" s="7"/>
       <c r="R5" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S5" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T5" s="7"/>
       <c r="U5" s="7"/>
@@ -25330,10 +25655,10 @@
       </c>
       <c r="Q6" s="7"/>
       <c r="R6" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S6" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T6" s="7"/>
       <c r="U6" s="7"/>
@@ -25444,10 +25769,10 @@
       </c>
       <c r="Q8" s="7"/>
       <c r="R8" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S8" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T8" s="7"/>
       <c r="U8" s="7"/>
@@ -25499,10 +25824,10 @@
         <v>326</v>
       </c>
       <c r="M9" s="7" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="N9" s="8" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="O9" s="7"/>
       <c r="P9" s="7">
@@ -25510,10 +25835,10 @@
       </c>
       <c r="Q9" s="7"/>
       <c r="R9" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S9" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T9" s="7"/>
       <c r="U9" s="7"/>
@@ -25620,10 +25945,10 @@
       </c>
       <c r="Q11" s="7"/>
       <c r="R11" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S11" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T11" s="7"/>
       <c r="U11" s="7"/>
@@ -25679,10 +26004,10 @@
       </c>
       <c r="Q12" s="7"/>
       <c r="R12" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S12" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T12" s="7"/>
       <c r="U12" s="7"/>
@@ -25738,10 +26063,10 @@
       </c>
       <c r="Q13" s="7"/>
       <c r="R13" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S13" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T13" s="7"/>
       <c r="U13" s="7"/>
@@ -25787,10 +26112,10 @@
       <c r="P14" s="7"/>
       <c r="Q14" s="7"/>
       <c r="R14" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S14" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T14" s="7"/>
       <c r="U14" s="7"/>
@@ -25846,10 +26171,10 @@
       </c>
       <c r="Q15" s="7"/>
       <c r="R15" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S15" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T15" s="7"/>
       <c r="U15" s="7"/>
@@ -25895,10 +26220,10 @@
       <c r="P16" s="7"/>
       <c r="Q16" s="7"/>
       <c r="R16" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S16" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T16" s="7"/>
       <c r="U16" s="7"/>
@@ -25944,10 +26269,10 @@
       <c r="P17" s="7"/>
       <c r="Q17" s="7"/>
       <c r="R17" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S17" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T17" s="7"/>
       <c r="U17" s="7"/>
@@ -25993,10 +26318,10 @@
       <c r="P18" s="7"/>
       <c r="Q18" s="7"/>
       <c r="R18" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S18" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T18" s="7"/>
       <c r="U18" s="7"/>
@@ -26052,10 +26377,10 @@
       </c>
       <c r="Q19" s="7"/>
       <c r="R19" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S19" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T19" s="7"/>
       <c r="U19" s="7"/>
@@ -26111,10 +26436,10 @@
       </c>
       <c r="Q20" s="7"/>
       <c r="R20" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S20" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T20" s="7"/>
       <c r="U20" s="7"/>
@@ -26163,10 +26488,10 @@
       <c r="P21" s="7"/>
       <c r="Q21" s="7"/>
       <c r="R21" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S21" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T21" s="7"/>
       <c r="U21" s="7"/>
@@ -26227,10 +26552,10 @@
       </c>
       <c r="Q22" s="7"/>
       <c r="R22" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S22" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T22" s="7"/>
       <c r="U22" s="7"/>
@@ -26286,10 +26611,10 @@
       </c>
       <c r="Q23" s="7"/>
       <c r="R23" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S23" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T23" s="7"/>
       <c r="U23" s="7"/>
@@ -26347,10 +26672,10 @@
       </c>
       <c r="Q24" s="7"/>
       <c r="R24" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S24" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T24" s="7"/>
       <c r="U24" s="7"/>
@@ -26406,10 +26731,10 @@
       </c>
       <c r="Q25" s="7"/>
       <c r="R25" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S25" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T25" s="7"/>
       <c r="U25" s="7"/>
@@ -26516,10 +26841,10 @@
       </c>
       <c r="Q27" s="7"/>
       <c r="R27" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S27" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T27" s="7"/>
       <c r="U27" s="7"/>
@@ -26575,10 +26900,10 @@
       </c>
       <c r="Q28" s="7"/>
       <c r="R28" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S28" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T28" s="7"/>
       <c r="U28" s="7"/>
@@ -26634,10 +26959,10 @@
       </c>
       <c r="Q29" s="7"/>
       <c r="R29" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S29" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T29" s="7"/>
       <c r="U29" s="7"/>
@@ -26744,10 +27069,10 @@
       </c>
       <c r="Q31" s="7"/>
       <c r="R31" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S31" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T31" s="7"/>
       <c r="U31" s="7"/>
@@ -26803,10 +27128,10 @@
       </c>
       <c r="Q32" s="7"/>
       <c r="R32" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S32" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T32" s="7"/>
       <c r="U32" s="7"/>
@@ -26852,10 +27177,10 @@
       <c r="P33" s="7"/>
       <c r="Q33" s="7"/>
       <c r="R33" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S33" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T33" s="7"/>
       <c r="U33" s="7"/>
@@ -26901,10 +27226,10 @@
       <c r="P34" s="7"/>
       <c r="Q34" s="7"/>
       <c r="R34" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S34" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T34" s="7"/>
       <c r="U34" s="7"/>
@@ -26960,10 +27285,10 @@
       </c>
       <c r="Q35" s="7"/>
       <c r="R35" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S35" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T35" s="7"/>
       <c r="U35" s="7"/>
@@ -27075,10 +27400,10 @@
       </c>
       <c r="Q37" s="7"/>
       <c r="R37" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S37" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T37" s="7"/>
       <c r="U37" s="7"/>
@@ -27127,10 +27452,10 @@
       <c r="P38" s="7"/>
       <c r="Q38" s="7"/>
       <c r="R38" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S38" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T38" s="7"/>
       <c r="U38" s="7"/>
@@ -27186,10 +27511,10 @@
       </c>
       <c r="Q39" s="7"/>
       <c r="R39" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S39" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T39" s="7"/>
       <c r="U39" s="7"/>
@@ -27245,10 +27570,10 @@
       </c>
       <c r="Q40" s="7"/>
       <c r="R40" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S40" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T40" s="7"/>
       <c r="U40" s="7"/>
@@ -27304,10 +27629,10 @@
       </c>
       <c r="Q41" s="7"/>
       <c r="R41" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S41" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T41" s="7"/>
       <c r="U41" s="7"/>
@@ -27363,10 +27688,10 @@
       </c>
       <c r="Q42" s="7"/>
       <c r="R42" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S42" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T42" s="7"/>
       <c r="U42" s="7"/>
@@ -27422,10 +27747,10 @@
       </c>
       <c r="Q43" s="7"/>
       <c r="R43" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S43" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T43" s="7"/>
       <c r="U43" s="7"/>
@@ -27481,10 +27806,10 @@
       </c>
       <c r="Q44" s="7"/>
       <c r="R44" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S44" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T44" s="7"/>
       <c r="U44" s="7"/>
@@ -27530,10 +27855,10 @@
       <c r="P45" s="7"/>
       <c r="Q45" s="7"/>
       <c r="R45" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S45" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T45" s="7" t="s">
         <v>371</v>
@@ -27591,10 +27916,10 @@
       <c r="P46" s="7"/>
       <c r="Q46" s="7"/>
       <c r="R46" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S46" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T46" s="7"/>
       <c r="U46" s="7"/>
@@ -27694,10 +28019,10 @@
       <c r="P48" s="7"/>
       <c r="Q48" s="7"/>
       <c r="R48" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S48" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T48" s="7"/>
       <c r="U48" s="7"/>
@@ -27753,10 +28078,10 @@
       </c>
       <c r="Q49" s="7"/>
       <c r="R49" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S49" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T49" s="7"/>
       <c r="U49" s="7"/>
@@ -27812,10 +28137,10 @@
       </c>
       <c r="Q50" s="7"/>
       <c r="R50" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S50" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T50" s="7"/>
       <c r="U50" s="7"/>
@@ -27861,10 +28186,10 @@
       <c r="P51" s="7"/>
       <c r="Q51" s="7"/>
       <c r="R51" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S51" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T51" s="7"/>
       <c r="U51" s="7"/>
@@ -27920,10 +28245,10 @@
       </c>
       <c r="Q52" s="7"/>
       <c r="R52" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S52" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T52" s="7"/>
       <c r="U52" s="7"/>
@@ -27979,10 +28304,10 @@
       </c>
       <c r="Q53" s="7"/>
       <c r="R53" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S53" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T53" s="7"/>
       <c r="U53" s="7"/>
@@ -28038,10 +28363,10 @@
       </c>
       <c r="Q54" s="7"/>
       <c r="R54" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S54" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T54" s="7"/>
       <c r="U54" s="7"/>
@@ -28148,10 +28473,10 @@
       </c>
       <c r="Q56" s="7"/>
       <c r="R56" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S56" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T56" s="7"/>
       <c r="U56" s="7"/>
@@ -28258,10 +28583,10 @@
       </c>
       <c r="Q58" s="7"/>
       <c r="R58" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S58" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T58" s="7"/>
       <c r="U58" s="7"/>
@@ -28317,10 +28642,10 @@
       </c>
       <c r="Q59" s="7"/>
       <c r="R59" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S59" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T59" s="7"/>
       <c r="U59" s="7"/>
@@ -28366,10 +28691,10 @@
       <c r="P60" s="7"/>
       <c r="Q60" s="7"/>
       <c r="R60" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S60" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T60" s="7"/>
       <c r="U60" s="7"/>
@@ -28425,10 +28750,10 @@
       </c>
       <c r="Q61" s="7"/>
       <c r="R61" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S61" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T61" s="7"/>
       <c r="U61" s="7"/>
@@ -28484,10 +28809,10 @@
       </c>
       <c r="Q62" s="7"/>
       <c r="R62" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S62" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T62" s="7"/>
       <c r="U62" s="7"/>
@@ -28546,10 +28871,10 @@
       </c>
       <c r="Q63" s="7"/>
       <c r="R63" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S63" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T63" s="7"/>
       <c r="U63" s="7"/>
@@ -28595,10 +28920,10 @@
       <c r="P64" s="7"/>
       <c r="Q64" s="7"/>
       <c r="R64" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S64" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T64" s="7"/>
       <c r="U64" s="7"/>
@@ -28654,10 +28979,10 @@
       </c>
       <c r="Q65" s="7"/>
       <c r="R65" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S65" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T65" s="7"/>
       <c r="U65" s="7"/>
@@ -28703,10 +29028,10 @@
       <c r="P66" s="7"/>
       <c r="Q66" s="7"/>
       <c r="R66" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S66" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T66" s="7"/>
       <c r="U66" s="7"/>
@@ -28749,10 +29074,10 @@
       <c r="P67" s="7"/>
       <c r="Q67" s="7"/>
       <c r="R67" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S67" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T67" s="7"/>
       <c r="U67" s="7"/>
@@ -28889,6 +29214,10 @@
       <c r="S72" s="7"/>
     </row>
     <row r="73" spans="1:33">
+      <c r="F73">
+        <f>COUNTIF(F2:F69,"Yes")</f>
+        <v>7</v>
+      </c>
       <c r="R73" s="7"/>
       <c r="S73" s="7"/>
     </row>
@@ -28936,19 +29265,8 @@
       <c r="R84" s="7"/>
       <c r="S84" s="7"/>
     </row>
-    <row r="85" spans="18:19">
-      <c r="R85" s="7"/>
-      <c r="S85" s="7"/>
-    </row>
-    <row r="86" spans="18:19">
-      <c r="R86" s="7"/>
-      <c r="S86" s="7"/>
-    </row>
-    <row r="87" spans="18:19">
-      <c r="R87" s="7"/>
-      <c r="S87" s="7"/>
-    </row>
   </sheetData>
+  <autoFilter ref="A1:AG1" xr:uid="{A51AA501-5C31-4DF1-B0EE-7C895471879E}"/>
   <conditionalFormatting sqref="G2:G69">
     <cfRule type="expression" dxfId="302" priority="4">
       <formula>$I2&lt;&gt;""</formula>
@@ -28994,7 +29312,7 @@
       <formula>OR($I2="Addition",$I2="Omission",$I2 = "Substitution - Word")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:S69 R70:S87">
+  <conditionalFormatting sqref="Q2:S69 R70:S84">
     <cfRule type="expression" dxfId="291" priority="1">
       <formula>AND(AND(LEFT($I2,3)="Sub", RIGHT($I2,4)&lt;&gt;"Form"),$S2&lt;&gt;"")</formula>
     </cfRule>
@@ -29051,6 +29369,12 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="15">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{E23A157A-5E01-4994-8264-037B2440CA9E}">
+          <x14:formula1>
+            <xm:f>'Data Regularization'!$Q$2:$Q$4</xm:f>
+          </x14:formula1>
+          <xm:sqref>AD2:AD69 AF2:AF69</xm:sqref>
+        </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C57CBA19-B2A7-4370-B83A-A8B3384F1D19}">
           <x14:formula1>
             <xm:f>'Data Regularization'!$D$2:$D$1048576</xm:f>
@@ -29077,49 +29401,49 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{931200A1-084C-41D1-8503-F253C95CF4C2}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$J$2:$J$1048576</xm:f>
+            <xm:f>'Data Regularization'!$K$2:$K$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>T2:T69 V2:V69</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{E0642AF3-ED54-4F60-9479-EC4C0C64717D}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$K$2:$K$1048576</xm:f>
+            <xm:f>'Data Regularization'!$L$2:$L$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>W2:W69</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{2CADAAFC-84A9-4A8C-99CC-7D1509F55488}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$L$2:$L$1048576</xm:f>
+            <xm:f>'Data Regularization'!$M$2:$M$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>X2:X69</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{8F864FD0-C10C-4848-9226-655314C3389C}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$M$2:$M$1048576</xm:f>
+            <xm:f>'Data Regularization'!$N$2:$N$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>Y2:Y69</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{FB4BD7DE-5248-427B-A541-C15B1A957CC0}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$N$2:$N$1048576</xm:f>
+            <xm:f>'Data Regularization'!$O$2:$O$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AA2:AA69</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{7B010774-7EE5-4DDA-B23F-253ACDC9C866}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$O$2:$O$1048576</xm:f>
+            <xm:f>'Data Regularization'!$P$2:$P$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AB2:AB69</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{EC9DC2E8-182F-462D-AAC4-61BD52B5D75D}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$P$2:$P$1048576</xm:f>
+            <xm:f>'Data Regularization'!$Q$2:$Q$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AC2:AC69</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{308A9869-BCC6-469C-AEA8-65A229F1F852}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$C$2:$C$50</xm:f>
+            <xm:f>'Data Regularization'!$C$2:$C$29</xm:f>
           </x14:formula1>
           <xm:sqref>F2:F69</xm:sqref>
         </x14:dataValidation>
@@ -29135,12 +29459,6 @@
           </x14:formula1>
           <xm:sqref>E2:E69</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{E23A157A-5E01-4994-8264-037B2440CA9E}">
-          <x14:formula1>
-            <xm:f>'Data Regularization'!$P$2:$P$4</xm:f>
-          </x14:formula1>
-          <xm:sqref>AD2:AD69 AF2:AF69</xm:sqref>
-        </x14:dataValidation>
       </x14:dataValidations>
     </ext>
   </extLst>
@@ -29149,7 +29467,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75227B9B-1339-4A7F-9A7F-95454CF244EB}">
-  <dimension ref="A1:AH112"/>
+  <dimension ref="A1:AH124"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:34" s="1" customFormat="1" ht="29">
@@ -29202,16 +29520,16 @@
         <v>363</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="R1" s="1" t="s">
         <v>364</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="U1" s="1" t="s">
         <v>367</v>
@@ -29258,7 +29576,7 @@
         <v>38</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>158</v>
@@ -29291,10 +29609,10 @@
       </c>
       <c r="R2" s="7"/>
       <c r="S2" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T2" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U2" s="7"/>
       <c r="V2" s="7"/>
@@ -29358,10 +29676,10 @@
       </c>
       <c r="R3" s="7"/>
       <c r="S3" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T3" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U3" s="7"/>
       <c r="V3" s="7"/>
@@ -29421,10 +29739,10 @@
       </c>
       <c r="R4" s="7"/>
       <c r="S4" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T4" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U4" s="7"/>
       <c r="V4" s="7"/>
@@ -29484,10 +29802,10 @@
       </c>
       <c r="R5" s="7"/>
       <c r="S5" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T5" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U5" s="7"/>
       <c r="V5" s="7"/>
@@ -29551,10 +29869,10 @@
       </c>
       <c r="R6" s="7"/>
       <c r="S6" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T6" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U6" s="7"/>
       <c r="V6" s="7"/>
@@ -29606,10 +29924,10 @@
         <v>326</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="N7" s="8" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="O7" s="7"/>
       <c r="P7" s="7">
@@ -29621,10 +29939,10 @@
       </c>
       <c r="R7" s="7"/>
       <c r="S7" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T7" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U7" s="7"/>
       <c r="V7" s="7"/>
@@ -29684,10 +30002,10 @@
       </c>
       <c r="R8" s="7"/>
       <c r="S8" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T8" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U8" s="7"/>
       <c r="V8" s="7"/>
@@ -29747,10 +30065,10 @@
       </c>
       <c r="R9" s="7"/>
       <c r="S9" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T9" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U9" s="7"/>
       <c r="V9" s="7"/>
@@ -29810,10 +30128,10 @@
       </c>
       <c r="R10" s="7"/>
       <c r="S10" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T10" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U10" s="7"/>
       <c r="V10" s="7"/>
@@ -29873,10 +30191,10 @@
       </c>
       <c r="R11" s="7"/>
       <c r="S11" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T11" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U11" s="7"/>
       <c r="V11" s="7"/>
@@ -29936,10 +30254,10 @@
       </c>
       <c r="R12" s="7"/>
       <c r="S12" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T12" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U12" s="7"/>
       <c r="V12" s="7"/>
@@ -29999,10 +30317,10 @@
       </c>
       <c r="R13" s="7"/>
       <c r="S13" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T13" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U13" s="7"/>
       <c r="V13" s="7"/>
@@ -30067,10 +30385,10 @@
       </c>
       <c r="R14" s="7"/>
       <c r="S14" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T14" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U14" s="7"/>
       <c r="V14" s="7"/>
@@ -30130,10 +30448,10 @@
       </c>
       <c r="R15" s="7"/>
       <c r="S15" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T15" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U15" s="7"/>
       <c r="V15" s="7"/>
@@ -30195,10 +30513,10 @@
       </c>
       <c r="R16" s="7"/>
       <c r="S16" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T16" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U16" s="7"/>
       <c r="V16" s="7"/>
@@ -30258,10 +30576,10 @@
       </c>
       <c r="R17" s="7"/>
       <c r="S17" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T17" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U17" s="7"/>
       <c r="V17" s="7"/>
@@ -30321,10 +30639,10 @@
       </c>
       <c r="R18" s="7"/>
       <c r="S18" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T18" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U18" s="7"/>
       <c r="V18" s="7"/>
@@ -30384,10 +30702,10 @@
       </c>
       <c r="R19" s="7"/>
       <c r="S19" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T19" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U19" s="7"/>
       <c r="V19" s="7"/>
@@ -30409,7 +30727,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:34" ht="58">
+    <row r="20" spans="1:34" ht="72.5">
       <c r="A20" t="s">
         <v>89</v>
       </c>
@@ -30447,10 +30765,10 @@
       </c>
       <c r="R20" s="7"/>
       <c r="S20" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T20" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U20" s="7"/>
       <c r="V20" s="7"/>
@@ -30510,10 +30828,10 @@
       </c>
       <c r="R21" s="7"/>
       <c r="S21" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T21" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U21" s="7"/>
       <c r="V21" s="7"/>
@@ -30573,10 +30891,10 @@
       </c>
       <c r="R22" s="7"/>
       <c r="S22" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T22" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U22" s="7"/>
       <c r="V22" s="7"/>
@@ -30636,10 +30954,10 @@
       </c>
       <c r="R23" s="7"/>
       <c r="S23" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T23" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U23" s="7"/>
       <c r="V23" s="7"/>
@@ -30661,7 +30979,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:34" ht="275.5">
+    <row r="24" spans="1:34" ht="290">
       <c r="A24" t="s">
         <v>99</v>
       </c>
@@ -30704,10 +31022,10 @@
       </c>
       <c r="R24" s="7"/>
       <c r="S24" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T24" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U24" s="7"/>
       <c r="V24" s="7"/>
@@ -30767,10 +31085,10 @@
       </c>
       <c r="R25" s="7"/>
       <c r="S25" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T25" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U25" s="7"/>
       <c r="V25" s="7"/>
@@ -30830,10 +31148,10 @@
       </c>
       <c r="R26" s="7"/>
       <c r="S26" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T26" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U26" s="7"/>
       <c r="V26" s="7"/>
@@ -30893,10 +31211,10 @@
       </c>
       <c r="R27" s="7"/>
       <c r="S27" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T27" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U27" s="7"/>
       <c r="V27" s="7"/>
@@ -30956,10 +31274,10 @@
       </c>
       <c r="R28" s="7"/>
       <c r="S28" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T28" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U28" s="7"/>
       <c r="V28" s="7"/>
@@ -30981,7 +31299,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:34" ht="72.5">
+    <row r="29" spans="1:34" ht="87">
       <c r="A29" t="s">
         <v>112</v>
       </c>
@@ -31019,10 +31337,10 @@
       </c>
       <c r="R29" s="7"/>
       <c r="S29" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T29" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U29" s="7"/>
       <c r="V29" s="7"/>
@@ -31044,7 +31362,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:34" ht="43.5">
+    <row r="30" spans="1:34" ht="58">
       <c r="A30" t="s">
         <v>115</v>
       </c>
@@ -31082,10 +31400,10 @@
       </c>
       <c r="R30" s="7"/>
       <c r="S30" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T30" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U30" s="7"/>
       <c r="V30" s="7"/>
@@ -31107,7 +31425,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:34" ht="145">
+    <row r="31" spans="1:34" ht="159.5">
       <c r="A31" t="s">
         <v>125</v>
       </c>
@@ -31145,10 +31463,10 @@
       </c>
       <c r="R31" s="7"/>
       <c r="S31" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T31" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U31" s="7"/>
       <c r="V31" s="7"/>
@@ -31170,7 +31488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:34" ht="159.5">
+    <row r="32" spans="1:34" ht="174">
       <c r="A32" t="s">
         <v>129</v>
       </c>
@@ -31208,10 +31526,10 @@
       </c>
       <c r="R32" s="7"/>
       <c r="S32" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T32" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U32" s="7"/>
       <c r="V32" s="7"/>
@@ -31271,10 +31589,10 @@
       </c>
       <c r="R33" s="7"/>
       <c r="S33" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T33" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U33" s="7"/>
       <c r="V33" s="7"/>
@@ -31334,10 +31652,10 @@
       </c>
       <c r="R34" s="7"/>
       <c r="S34" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T34" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U34" s="7"/>
       <c r="V34" s="7"/>
@@ -31397,10 +31715,10 @@
       </c>
       <c r="R35" s="7"/>
       <c r="S35" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T35" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U35" s="7"/>
       <c r="V35" s="7"/>
@@ -31460,10 +31778,10 @@
       </c>
       <c r="R36" s="7"/>
       <c r="S36" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T36" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U36" s="7"/>
       <c r="V36" s="7"/>
@@ -31523,10 +31841,10 @@
       </c>
       <c r="R37" s="7"/>
       <c r="S37" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T37" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U37" s="7"/>
       <c r="V37" s="7"/>
@@ -31586,10 +31904,10 @@
       </c>
       <c r="R38" s="7"/>
       <c r="S38" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T38" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U38" s="7"/>
       <c r="V38" s="7"/>
@@ -31649,10 +31967,10 @@
       </c>
       <c r="R39" s="7"/>
       <c r="S39" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T39" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U39" s="7"/>
       <c r="V39" s="7"/>
@@ -31712,10 +32030,10 @@
       </c>
       <c r="R40" s="7"/>
       <c r="S40" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T40" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U40" s="7"/>
       <c r="V40" s="7"/>
@@ -31775,10 +32093,10 @@
       </c>
       <c r="R41" s="7"/>
       <c r="S41" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T41" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U41" s="7"/>
       <c r="V41" s="7"/>
@@ -31800,7 +32118,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:34" ht="58">
+    <row r="42" spans="1:34" ht="72.5">
       <c r="A42" t="s">
         <v>152</v>
       </c>
@@ -31841,10 +32159,10 @@
       </c>
       <c r="R42" s="7"/>
       <c r="S42" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T42" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U42" s="7"/>
       <c r="V42" s="7"/>
@@ -31904,10 +32222,10 @@
       </c>
       <c r="R43" s="7"/>
       <c r="S43" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T43" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U43" s="7"/>
       <c r="V43" s="7"/>
@@ -31939,7 +32257,7 @@
     </row>
     <row r="46" spans="1:34">
       <c r="E46" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="F46">
         <f>COUNTIF(G:G,"Addition")</f>
@@ -31950,13 +32268,13 @@
     </row>
     <row r="47" spans="1:34">
       <c r="B47" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C47" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E47" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F47">
         <f>COUNTIF(G:G,"Omission")</f>
@@ -31973,7 +32291,7 @@
         <v>325</v>
       </c>
       <c r="E48" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F48">
         <f>F46/(F46+F47)</f>
@@ -32010,7 +32328,7 @@
         <v>352</v>
       </c>
       <c r="E51" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F51">
         <f>COUNTIFS(G:G,"Addition", K:K,"Article")+COUNTIFS(G:G,"Addition", K:K,"Conjunction")+COUNTIFS(G:G,"Addition", K:K,"Pronoun")+COUNTIFS(G:G,"Addition", K:K,"Preposition")+COUNTIFS(G:G,"Addition", K:K,"Particle")+COUNTIFS(G:G,"Addition", K:K,"Vocative")</f>
@@ -32027,7 +32345,7 @@
         <v>383</v>
       </c>
       <c r="E52" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F52">
         <f>COUNTIFS(G:G,"Omission", K:K,"Article")+COUNTIFS(G:G,"Omission", K:K,"Conjunction")+COUNTIFS(G:G,"Omission", K:K,"Pronoun")+COUNTIFS(G:G,"Omission", K:K,"Preposition")+COUNTIFS(G:G,"Omission", K:K,"Particle")+COUNTIFS(G:G,"Omission", K:K,"Vocative")</f>
@@ -32041,7 +32359,7 @@
         <v>353</v>
       </c>
       <c r="E53" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F53">
         <f>F51/(F51+F52)</f>
@@ -32060,7 +32378,7 @@
     </row>
     <row r="56" spans="2:20">
       <c r="E56" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F56">
         <f>COUNTIFS(G:G,"Addition", K:K,"Adjective")+COUNTIFS(G:G,"Addition", K:K,"Adverb")+COUNTIFS(G:G,"Addition", K:K,"Noun")+COUNTIFS(G:G,"Addition", K:K,"Participle")+COUNTIFS(G:G,"Addition", K:K,"Verb")</f>
@@ -32071,7 +32389,7 @@
     </row>
     <row r="57" spans="2:20">
       <c r="E57" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F57">
         <f>COUNTIFS(G:G,"Omission", K:K,"Adjective")+COUNTIFS(G:G,"Omission", K:K,"Adverb")+COUNTIFS(G:G,"Omission", K:K,"Noun")+COUNTIFS(G:G,"Omission", K:K,"Participle")+COUNTIFS(G:G,"Omission", K:K,"Verb")</f>
@@ -32082,7 +32400,7 @@
     </row>
     <row r="58" spans="2:20">
       <c r="E58" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="F58">
         <f>F56/(F56+F57)</f>
@@ -32093,7 +32411,7 @@
     </row>
     <row r="59" spans="2:20">
       <c r="E59" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="F59">
         <f>F58-F53</f>
@@ -32112,7 +32430,7 @@
     </row>
     <row r="62" spans="2:20">
       <c r="D62" s="11" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E62" s="11"/>
       <c r="F62" s="11"/>
@@ -32124,17 +32442,17 @@
         <v>326</v>
       </c>
       <c r="E63" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="F63" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="S63" s="7"/>
       <c r="T63" s="7"/>
     </row>
     <row r="64" spans="2:20">
       <c r="C64" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D64">
         <f>COUNTIFS(G:G,"Addition", L:L, "Present")</f>
@@ -32153,7 +32471,7 @@
     </row>
     <row r="65" spans="3:20">
       <c r="C65" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D65">
         <f>COUNTIFS(G:G,"Omission", L:L, "Present")</f>
@@ -32172,7 +32490,7 @@
     </row>
     <row r="66" spans="3:20">
       <c r="C66" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D66">
         <f>SUM(D64+D65)</f>
@@ -32199,20 +32517,20 @@
     </row>
     <row r="69" spans="3:20">
       <c r="D69" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E69" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F69" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="S69" s="7"/>
       <c r="T69" s="7"/>
     </row>
     <row r="70" spans="3:20">
       <c r="C70" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D70">
         <f>COUNTIFS(G:G,"Addition", L:L, "Absent")</f>
@@ -32231,7 +32549,7 @@
     </row>
     <row r="71" spans="3:20">
       <c r="C71" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D71">
         <f>COUNTIFS(G:G,"Addition", L:L, "Present")</f>
@@ -32250,7 +32568,7 @@
     </row>
     <row r="72" spans="3:20">
       <c r="E72" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="F72">
         <f>F71-F70</f>
@@ -32269,20 +32587,20 @@
     </row>
     <row r="75" spans="3:20">
       <c r="D75" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E75" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F75" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="S75" s="7"/>
       <c r="T75" s="7"/>
     </row>
     <row r="76" spans="3:20">
       <c r="C76" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D76">
         <f>COUNTIFS(G:G,"Addition", O:O, "")</f>
@@ -32301,7 +32619,7 @@
     </row>
     <row r="77" spans="3:20">
       <c r="C77" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D77">
         <f>COUNTIFS(G:G,"Addition", O:O, "Dittography")</f>
@@ -32320,7 +32638,7 @@
     </row>
     <row r="78" spans="3:20">
       <c r="E78" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="F78">
         <f>F77-F76</f>
@@ -32339,16 +32657,16 @@
     </row>
     <row r="81" spans="3:20">
       <c r="C81" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D81" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E81" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F81" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="S81" s="7"/>
       <c r="T81" s="7"/>
@@ -32374,7 +32692,7 @@
     </row>
     <row r="83" spans="3:20">
       <c r="C83" s="9" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D83">
         <f>COUNTIFS(G:G,"Addition", I:I, "&gt;=2", I:I, "&lt;=3")</f>
@@ -32393,7 +32711,7 @@
     </row>
     <row r="84" spans="3:20">
       <c r="C84" s="9" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D84">
         <f>COUNTIFS(G:G,"Addition", I:I, "&gt;=4")</f>
@@ -32420,16 +32738,16 @@
     </row>
     <row r="87" spans="3:20">
       <c r="C87" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D87" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E87" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F87" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="S87" s="7"/>
       <c r="T87" s="7"/>
@@ -32512,7 +32830,7 @@
     </row>
     <row r="92" spans="3:20">
       <c r="C92" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D92" s="9">
         <f>COUNTIFS(G:G,"Addition", I:I, C92)</f>
@@ -32540,7 +32858,7 @@
     </row>
     <row r="95" spans="3:20">
       <c r="E95" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="F95">
         <v>20338</v>
@@ -32615,6 +32933,54 @@
     <row r="112" spans="19:20">
       <c r="S112" s="7"/>
       <c r="T112" s="7"/>
+    </row>
+    <row r="113" spans="19:20">
+      <c r="S113" s="7"/>
+      <c r="T113" s="7"/>
+    </row>
+    <row r="114" spans="19:20">
+      <c r="S114" s="7"/>
+      <c r="T114" s="7"/>
+    </row>
+    <row r="115" spans="19:20">
+      <c r="S115" s="7"/>
+      <c r="T115" s="7"/>
+    </row>
+    <row r="116" spans="19:20">
+      <c r="S116" s="7"/>
+      <c r="T116" s="7"/>
+    </row>
+    <row r="117" spans="19:20">
+      <c r="S117" s="7"/>
+      <c r="T117" s="7"/>
+    </row>
+    <row r="118" spans="19:20">
+      <c r="S118" s="7"/>
+      <c r="T118" s="7"/>
+    </row>
+    <row r="119" spans="19:20">
+      <c r="S119" s="7"/>
+      <c r="T119" s="7"/>
+    </row>
+    <row r="120" spans="19:20">
+      <c r="S120" s="7"/>
+      <c r="T120" s="7"/>
+    </row>
+    <row r="121" spans="19:20">
+      <c r="S121" s="7"/>
+      <c r="T121" s="7"/>
+    </row>
+    <row r="122" spans="19:20">
+      <c r="S122" s="7"/>
+      <c r="T122" s="7"/>
+    </row>
+    <row r="123" spans="19:20">
+      <c r="S123" s="7"/>
+      <c r="T123" s="7"/>
+    </row>
+    <row r="124" spans="19:20">
+      <c r="S124" s="7"/>
+      <c r="T124" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -32676,7 +33042,7 @@
       <formula>AND($I2&lt;&gt;"Addition",$I2&lt;&gt;"Omission",$I2&lt;&gt;"Substitution - Word")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:T43 S44:T112">
+  <conditionalFormatting sqref="R2:T43 S44:T124">
     <cfRule type="expression" dxfId="265" priority="4">
       <formula>AND(AND(LEFT($I2,3)="Sub", RIGHT($I2,4)&lt;&gt;"Form"),$T2&lt;&gt;"")</formula>
     </cfRule>
@@ -32734,6 +33100,12 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="15">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{28CA039E-CF90-4070-8DB7-6618F0092097}">
+          <x14:formula1>
+            <xm:f>'Data Regularization'!$Q$2:$Q$4</xm:f>
+          </x14:formula1>
+          <xm:sqref>AE2:AE43 AG2:AG43</xm:sqref>
+        </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{61092ACE-4CE5-4035-B1A4-FFD065D82F8D}">
           <x14:formula1>
             <xm:f>'Data Regularization'!$D$2:$D$1048576</xm:f>
@@ -32760,49 +33132,49 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{380F4392-57EF-4692-85DE-403E37D8100D}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$J$2:$J$1048576</xm:f>
+            <xm:f>'Data Regularization'!$K$2:$K$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>U2:U43 W2:W43</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{FC5D931A-A2D2-42BA-AA7F-C3341333AA2B}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$K$2:$K$1048576</xm:f>
+            <xm:f>'Data Regularization'!$L$2:$L$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>X2:X43</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{11C7590F-6026-4064-AC81-3A57A32DD135}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$L$2:$L$1048576</xm:f>
+            <xm:f>'Data Regularization'!$M$2:$M$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>Y2:Y43</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{1685823D-8DB6-45C5-8DD8-2EBCB3421A44}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$M$2:$M$1048576</xm:f>
+            <xm:f>'Data Regularization'!$N$2:$N$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>Z2:Z43</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{F2DA3C2F-619D-4179-80D3-D26C94D16253}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$N$2:$N$1048576</xm:f>
+            <xm:f>'Data Regularization'!$O$2:$O$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AB2:AB43</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{3D1076E6-3308-4CB7-9819-2F9E5BEA5CA6}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$O$2:$O$1048576</xm:f>
+            <xm:f>'Data Regularization'!$P$2:$P$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AC2:AC43</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{7CA3A2A1-BF41-44E3-AA42-2D39D252C40C}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$P$2:$P$1048576</xm:f>
+            <xm:f>'Data Regularization'!$Q$2:$Q$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AD2:AD43</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{433C2C66-0572-45BF-905B-346EC8EA9AEF}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$C$2:$C$50</xm:f>
+            <xm:f>'Data Regularization'!$C$2:$C$29</xm:f>
           </x14:formula1>
           <xm:sqref>F2:F43</xm:sqref>
         </x14:dataValidation>
@@ -32818,12 +33190,6 @@
           </x14:formula1>
           <xm:sqref>E2:E43</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{28CA039E-CF90-4070-8DB7-6618F0092097}">
-          <x14:formula1>
-            <xm:f>'Data Regularization'!$P$2:$P$4</xm:f>
-          </x14:formula1>
-          <xm:sqref>AE2:AE43 AG2:AG43</xm:sqref>
-        </x14:dataValidation>
       </x14:dataValidations>
     </ext>
   </extLst>
@@ -32885,16 +33251,16 @@
         <v>363</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="R1" s="1" t="s">
         <v>364</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="U1" s="1" t="s">
         <v>367</v>
@@ -32941,7 +33307,7 @@
         <v>38</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>158</v>
@@ -32973,10 +33339,10 @@
       </c>
       <c r="R2" s="7"/>
       <c r="S2" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T2" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U2" s="7"/>
       <c r="V2" s="7"/>
@@ -33039,10 +33405,10 @@
       </c>
       <c r="R3" s="7"/>
       <c r="S3" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T3" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U3" s="7"/>
       <c r="V3" s="7"/>
@@ -33101,10 +33467,10 @@
       </c>
       <c r="R4" s="7"/>
       <c r="S4" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T4" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U4" s="7"/>
       <c r="V4" s="7"/>
@@ -33163,10 +33529,10 @@
       </c>
       <c r="R5" s="7"/>
       <c r="S5" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T5" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U5" s="7"/>
       <c r="V5" s="7"/>
@@ -33229,10 +33595,10 @@
       </c>
       <c r="R6" s="7"/>
       <c r="S6" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T6" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U6" s="7"/>
       <c r="V6" s="7"/>
@@ -33291,10 +33657,10 @@
       </c>
       <c r="R7" s="7"/>
       <c r="S7" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T7" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U7" s="7"/>
       <c r="V7" s="7"/>
@@ -33353,10 +33719,10 @@
       </c>
       <c r="R8" s="7"/>
       <c r="S8" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T8" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U8" s="7"/>
       <c r="V8" s="7"/>
@@ -33415,10 +33781,10 @@
       </c>
       <c r="R9" s="7"/>
       <c r="S9" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T9" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U9" s="7"/>
       <c r="V9" s="7"/>
@@ -33477,10 +33843,10 @@
       </c>
       <c r="R10" s="7"/>
       <c r="S10" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T10" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U10" s="7"/>
       <c r="V10" s="7"/>
@@ -33539,10 +33905,10 @@
       </c>
       <c r="R11" s="7"/>
       <c r="S11" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T11" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U11" s="7"/>
       <c r="V11" s="7"/>
@@ -33601,10 +33967,10 @@
       </c>
       <c r="R12" s="7"/>
       <c r="S12" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T12" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U12" s="7"/>
       <c r="V12" s="7"/>
@@ -33663,10 +34029,10 @@
       </c>
       <c r="R13" s="7"/>
       <c r="S13" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T13" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U13" s="7"/>
       <c r="V13" s="7"/>
@@ -33727,10 +34093,10 @@
       </c>
       <c r="R14" s="7"/>
       <c r="S14" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T14" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U14" s="7"/>
       <c r="V14" s="7"/>
@@ -33789,10 +34155,10 @@
       </c>
       <c r="R15" s="7"/>
       <c r="S15" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T15" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U15" s="7"/>
       <c r="V15" s="7"/>
@@ -33851,10 +34217,10 @@
       </c>
       <c r="R16" s="7"/>
       <c r="S16" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T16" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U16" s="7"/>
       <c r="V16" s="7"/>
@@ -33913,10 +34279,10 @@
       </c>
       <c r="R17" s="7"/>
       <c r="S17" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T17" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U17" s="7"/>
       <c r="V17" s="7"/>
@@ -33938,7 +34304,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:34" ht="58">
+    <row r="18" spans="1:34" ht="72.5">
       <c r="A18" t="s">
         <v>89</v>
       </c>
@@ -33975,10 +34341,10 @@
       </c>
       <c r="R18" s="7"/>
       <c r="S18" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T18" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U18" s="7"/>
       <c r="V18" s="7"/>
@@ -34037,10 +34403,10 @@
       </c>
       <c r="R19" s="7"/>
       <c r="S19" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T19" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U19" s="7"/>
       <c r="V19" s="7"/>
@@ -34099,10 +34465,10 @@
       </c>
       <c r="R20" s="7"/>
       <c r="S20" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T20" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U20" s="7"/>
       <c r="V20" s="7"/>
@@ -34161,10 +34527,10 @@
       </c>
       <c r="R21" s="7"/>
       <c r="S21" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T21" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U21" s="7"/>
       <c r="V21" s="7"/>
@@ -34223,10 +34589,10 @@
       </c>
       <c r="R22" s="7"/>
       <c r="S22" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T22" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U22" s="7"/>
       <c r="V22" s="7"/>
@@ -34285,10 +34651,10 @@
       </c>
       <c r="R23" s="7"/>
       <c r="S23" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T23" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U23" s="7"/>
       <c r="V23" s="7"/>
@@ -34310,7 +34676,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:34" ht="72.5">
+    <row r="24" spans="1:34" ht="87">
       <c r="A24" t="s">
         <v>112</v>
       </c>
@@ -34347,10 +34713,10 @@
       </c>
       <c r="R24" s="7"/>
       <c r="S24" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T24" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U24" s="7"/>
       <c r="V24" s="7"/>
@@ -34372,7 +34738,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:34" ht="43.5">
+    <row r="25" spans="1:34" ht="58">
       <c r="A25" t="s">
         <v>115</v>
       </c>
@@ -34409,10 +34775,10 @@
       </c>
       <c r="R25" s="7"/>
       <c r="S25" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T25" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U25" s="7"/>
       <c r="V25" s="7"/>
@@ -34434,7 +34800,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:34" ht="159.5">
+    <row r="26" spans="1:34" ht="174">
       <c r="A26" t="s">
         <v>129</v>
       </c>
@@ -34471,10 +34837,10 @@
       </c>
       <c r="R26" s="7"/>
       <c r="S26" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T26" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U26" s="7"/>
       <c r="V26" s="7"/>
@@ -34533,10 +34899,10 @@
       </c>
       <c r="R27" s="7"/>
       <c r="S27" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T27" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U27" s="7"/>
       <c r="V27" s="7"/>
@@ -34595,10 +34961,10 @@
       </c>
       <c r="R28" s="7"/>
       <c r="S28" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T28" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U28" s="7"/>
       <c r="V28" s="7"/>
@@ -34657,10 +35023,10 @@
       </c>
       <c r="R29" s="7"/>
       <c r="S29" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T29" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U29" s="7"/>
       <c r="V29" s="7"/>
@@ -34719,10 +35085,10 @@
       </c>
       <c r="R30" s="7"/>
       <c r="S30" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T30" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U30" s="7"/>
       <c r="V30" s="7"/>
@@ -34781,10 +35147,10 @@
       </c>
       <c r="R31" s="7"/>
       <c r="S31" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T31" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U31" s="7"/>
       <c r="V31" s="7"/>
@@ -34843,10 +35209,10 @@
       </c>
       <c r="R32" s="7"/>
       <c r="S32" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T32" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U32" s="7"/>
       <c r="V32" s="7"/>
@@ -34905,10 +35271,10 @@
       </c>
       <c r="R33" s="7"/>
       <c r="S33" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T33" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U33" s="7"/>
       <c r="V33" s="7"/>
@@ -34967,10 +35333,10 @@
       </c>
       <c r="R34" s="7"/>
       <c r="S34" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T34" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U34" s="7"/>
       <c r="V34" s="7"/>
@@ -35029,10 +35395,10 @@
       </c>
       <c r="R35" s="7"/>
       <c r="S35" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T35" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U35" s="7"/>
       <c r="V35" s="7"/>
@@ -35112,7 +35478,7 @@
     </row>
     <row r="40" spans="1:34">
       <c r="D40" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="E40">
         <v>20338</v>
@@ -35120,7 +35486,7 @@
     </row>
     <row r="41" spans="1:34">
       <c r="D41" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E41">
         <f>MEDIAN(Q:Q)</f>
@@ -35129,19 +35495,19 @@
     </row>
     <row r="44" spans="1:34">
       <c r="D44" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E44">
         <f>COUNTIFS(G:G, "Addition", Q:Q, "&gt;=" &amp; $E$41)</f>
         <v>9</v>
       </c>
       <c r="F44" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="45" spans="1:34">
       <c r="D45" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="E45">
         <f>COUNTIFS(G:G, "Omission", Q:Q, "&gt;=" &amp; $E$41)</f>
@@ -35150,7 +35516,7 @@
     </row>
     <row r="46" spans="1:34">
       <c r="D46" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E46">
         <f>E44/(E44+E45)</f>
@@ -35159,7 +35525,7 @@
     </row>
     <row r="47" spans="1:34">
       <c r="D47" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E47">
         <f>COUNTIFS(G:G, "Addition", Q:Q, "&lt;" &amp; $E$41)</f>
@@ -35168,7 +35534,7 @@
     </row>
     <row r="48" spans="1:34">
       <c r="D48" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E48">
         <f>COUNTIFS(G:G, "Omission", Q:Q, "&lt;" &amp; $E$41)</f>
@@ -35177,7 +35543,7 @@
     </row>
     <row r="49" spans="4:5">
       <c r="D49" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E49">
         <f>E47/(E47+E48)</f>
@@ -35186,7 +35552,7 @@
     </row>
     <row r="52" spans="4:5">
       <c r="D52" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E52">
         <f>COUNTIFS(G:G, "Addition", K:K, "Article")</f>
@@ -35195,7 +35561,7 @@
     </row>
     <row r="53" spans="4:5">
       <c r="D53" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="E53">
         <f>COUNTIFS(G:G, "Omission", K:K, "Article")</f>
@@ -35204,7 +35570,7 @@
     </row>
     <row r="54" spans="4:5">
       <c r="D54" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E54">
         <f>COUNTIFS(G:G, "Addition", K:K, "Article")/(COUNTIFS(G:G, "Addition", K:K, "Article") + COUNTIFS(G:G, "Omission", K:K, "Article"))</f>
@@ -35349,9 +35715,9 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="15">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{9260D979-ED3C-44A9-947F-E1ED2D810981}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$P$2:$P$4</xm:f>
+            <xm:f>'Data Regularization'!$Q$2:$Q$4</xm:f>
           </x14:formula1>
-          <xm:sqref>AE36:AG37 AE2:AE35 AG2:AG35</xm:sqref>
+          <xm:sqref>AE36:AG37 AG2:AG35 AE2:AE35</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D77113DB-BB01-40C4-8CA3-1EAD8BE6BC94}">
           <x14:formula1>
@@ -35367,49 +35733,49 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{71A7A0B1-D151-4125-AADC-C55B97AE4D8B}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$C$2:$C$50</xm:f>
+            <xm:f>'Data Regularization'!$C$2:$C$29</xm:f>
           </x14:formula1>
           <xm:sqref>F2:F37</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{EC57F860-964C-4324-8F73-D833A2608978}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$P$2:$P$1048576</xm:f>
+            <xm:f>'Data Regularization'!$Q$2:$Q$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AD2:AD37</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{A752F9F0-367C-4054-A8FF-8F709EBD15A3}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$O$2:$O$1048576</xm:f>
+            <xm:f>'Data Regularization'!$P$2:$P$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AC2:AC37</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{29AC971D-FD69-4813-BF03-7F91AC904886}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$N$2:$N$1048576</xm:f>
+            <xm:f>'Data Regularization'!$O$2:$O$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AB2:AB37</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{ACA02654-FE60-4EA0-B27B-29B603E3DE55}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$M$2:$M$1048576</xm:f>
+            <xm:f>'Data Regularization'!$N$2:$N$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>Z2:Z37</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{73B90BAA-BC63-4776-859D-D45C0E8C8B0E}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$L$2:$L$1048576</xm:f>
+            <xm:f>'Data Regularization'!$M$2:$M$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>Y2:Y37</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{A3EDF8B9-8F36-4CC3-BE93-D5CB35430157}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$K$2:$K$1048576</xm:f>
+            <xm:f>'Data Regularization'!$L$2:$L$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>X2:X37</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{143CA09F-033B-494A-9026-F20B443C1AC0}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$J$2:$J$1048576</xm:f>
+            <xm:f>'Data Regularization'!$K$2:$K$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>U2:U37 W2:W37</xm:sqref>
         </x14:dataValidation>
@@ -35498,16 +35864,16 @@
         <v>363</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="R1" s="1" t="s">
         <v>364</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="U1" s="1" t="s">
         <v>367</v>
@@ -35579,10 +35945,10 @@
         <v>326</v>
       </c>
       <c r="M2" s="7" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="N2" s="8" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="O2" s="7"/>
       <c r="P2" s="7">
@@ -35593,10 +35959,10 @@
       </c>
       <c r="R2" s="7"/>
       <c r="S2" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T2" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U2" s="7"/>
       <c r="V2" s="7"/>
@@ -35655,10 +36021,10 @@
       </c>
       <c r="R3" s="7"/>
       <c r="S3" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T3" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U3" s="7"/>
       <c r="V3" s="7"/>
@@ -35717,10 +36083,10 @@
       </c>
       <c r="R4" s="7"/>
       <c r="S4" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T4" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U4" s="7"/>
       <c r="V4" s="7"/>
@@ -35779,10 +36145,10 @@
       </c>
       <c r="R5" s="7"/>
       <c r="S5" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T5" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U5" s="7"/>
       <c r="V5" s="7"/>
@@ -35806,7 +36172,7 @@
     </row>
     <row r="8" spans="1:34">
       <c r="D8" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="E8">
         <v>20338</v>
@@ -35814,7 +36180,7 @@
     </row>
     <row r="9" spans="1:34">
       <c r="D9" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E9">
         <f>MEDIAN(Q:Q)</f>
@@ -35823,19 +36189,19 @@
     </row>
     <row r="12" spans="1:34">
       <c r="D12" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E12">
         <f>COUNTIFS(G:G, "Addition", Q:Q, "&gt;=" &amp; $E$9)</f>
         <v>0</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="13" spans="1:34">
       <c r="D13" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="E13">
         <f>COUNTIFS(G:G, "Omission", Q:Q, "&gt;=" &amp; $E$9)</f>
@@ -35844,7 +36210,7 @@
     </row>
     <row r="14" spans="1:34">
       <c r="D14" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E14">
         <f>E12/(E12+E13)</f>
@@ -35853,7 +36219,7 @@
     </row>
     <row r="15" spans="1:34">
       <c r="D15" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E15">
         <f>COUNTIFS(G:G, "Addition", Q:Q, "&lt;" &amp; $E$9)</f>
@@ -35862,7 +36228,7 @@
     </row>
     <row r="16" spans="1:34">
       <c r="D16" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E16">
         <f>COUNTIFS(G:G, "Omission", Q:Q, "&lt;" &amp; $E$9)</f>
@@ -35871,7 +36237,7 @@
     </row>
     <row r="17" spans="4:5">
       <c r="D17" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E17">
         <f>E15/(E15+E16)</f>
@@ -35880,7 +36246,7 @@
     </row>
     <row r="18" spans="4:5">
       <c r="D18" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E18">
         <f>E14-E17</f>
@@ -36002,7 +36368,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="15">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{245942D1-D075-4E5A-AA7D-9C26721C81CC}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$P$2:$P$4</xm:f>
+            <xm:f>'Data Regularization'!$Q$2:$Q$4</xm:f>
           </x14:formula1>
           <xm:sqref>AE2:AE5 AG2:AG5</xm:sqref>
         </x14:dataValidation>
@@ -36020,49 +36386,49 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{0C1A181C-3A1B-44D6-9AEF-E7B5139C83B9}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$C$2:$C$50</xm:f>
+            <xm:f>'Data Regularization'!$C$2:$C$29</xm:f>
           </x14:formula1>
           <xm:sqref>F2:F5</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{0D7F4E81-0669-4267-8383-11B490BA185B}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$P$2:$P$1048576</xm:f>
+            <xm:f>'Data Regularization'!$Q$2:$Q$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AD2:AD5</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D88E8866-7F09-4C46-97E8-AA2A6B2667E1}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$O$2:$O$1048576</xm:f>
+            <xm:f>'Data Regularization'!$P$2:$P$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AC2:AC5</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{6C0E0DF9-2506-42B6-AC96-1041F2D47BA0}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$N$2:$N$1048576</xm:f>
+            <xm:f>'Data Regularization'!$O$2:$O$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AB2:AB5</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{2A61E2C9-3172-4379-8C63-C9EAC76F2AE2}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$M$2:$M$1048576</xm:f>
+            <xm:f>'Data Regularization'!$N$2:$N$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>Z2:Z5</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{2F52DEFB-15A6-4B83-9BF9-7F3CC450E71A}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$L$2:$L$1048576</xm:f>
+            <xm:f>'Data Regularization'!$M$2:$M$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>Y2:Y5</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{5E9D2A79-9D05-42FB-B793-427B83F59A93}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$K$2:$K$1048576</xm:f>
+            <xm:f>'Data Regularization'!$L$2:$L$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>X2:X5</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{CAF098A5-35B7-41DF-9A9D-C3CD42E80A57}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$J$2:$J$1048576</xm:f>
+            <xm:f>'Data Regularization'!$K$2:$K$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>U2:U5 W2:W5</xm:sqref>
         </x14:dataValidation>
@@ -36154,19 +36520,19 @@
         <v>364</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="W1" s="1" t="s">
         <v>367</v>
@@ -36397,7 +36763,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:36" ht="58">
+    <row r="5" spans="1:36" ht="72.5">
       <c r="A5" t="s">
         <v>89</v>
       </c>
@@ -36843,7 +37209,7 @@
     </row>
     <row r="14" spans="1:36">
       <c r="D14" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="E14">
         <v>20338</v>
@@ -36851,7 +37217,7 @@
     </row>
     <row r="17" spans="4:5">
       <c r="D17" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E17">
         <f>COUNTIF(Q:Q, "&gt;0")</f>
@@ -36860,7 +37226,7 @@
     </row>
     <row r="18" spans="4:5">
       <c r="D18" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E18">
         <f>COUNTIF(Q:Q, "&lt;0")</f>
@@ -36869,7 +37235,7 @@
     </row>
     <row r="19" spans="4:5">
       <c r="D19" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E19">
         <f>_xlfn.BINOM.DIST(MIN(E17,E18),(E17+E18),0.5,TRUE)*2</f>
@@ -36878,7 +37244,7 @@
     </row>
     <row r="21" spans="4:5">
       <c r="D21" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E21">
         <f>AVERAGE(Q:Q)</f>
@@ -36887,7 +37253,7 @@
     </row>
     <row r="22" spans="4:5">
       <c r="D22" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="E22">
         <f>_xlfn.STDEV.S(Q:Q)</f>
@@ -36896,7 +37262,7 @@
     </row>
     <row r="25" spans="4:5">
       <c r="D25" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="E25">
         <f>AVERAGE(V:V)</f>
@@ -36905,7 +37271,7 @@
     </row>
     <row r="26" spans="4:5">
       <c r="D26" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="E26">
         <f>_xlfn.STDEV.S(V:V)</f>
@@ -36914,7 +37280,7 @@
     </row>
     <row r="29" spans="4:5">
       <c r="D29" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E29">
         <f>COUNT(V:V)</f>
@@ -36923,7 +37289,7 @@
     </row>
     <row r="30" spans="4:5">
       <c r="D30" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E30">
         <f>_xlfn.STDEV.P(V:V)</f>
@@ -37033,6 +37399,12 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="15">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{3C3E11D3-993B-43FD-A727-064A9E0FE648}">
+          <x14:formula1>
+            <xm:f>'Data Regularization'!$Q$2:$Q$4</xm:f>
+          </x14:formula1>
+          <xm:sqref>AG2:AG11 AI2:AI11</xm:sqref>
+        </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{EB683865-3860-4E79-807A-77C6FE098E0E}">
           <x14:formula1>
             <xm:f>'Data Regularization'!$D$2:$D$1048576</xm:f>
@@ -37059,49 +37431,49 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{162F021C-F0F4-4DDF-B88C-CE3D8FE7097D}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$J$2:$J$1048576</xm:f>
+            <xm:f>'Data Regularization'!$K$2:$K$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>W2:W11 Y2:Y11</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{416FF628-8DCE-4DC2-81A8-8A334149DA53}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$K$2:$K$1048576</xm:f>
+            <xm:f>'Data Regularization'!$L$2:$L$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>Z2:Z11</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{6F081285-9AFC-469D-AE56-41F0B5B34757}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$L$2:$L$1048576</xm:f>
+            <xm:f>'Data Regularization'!$M$2:$M$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AA2:AA11</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{E74176C8-0AD1-43D6-B123-F757B2A6CD62}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$M$2:$M$1048576</xm:f>
+            <xm:f>'Data Regularization'!$N$2:$N$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AB2:AB11</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{DF9CF9CF-24C8-4B93-9990-7C6D10D94539}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$N$2:$N$1048576</xm:f>
+            <xm:f>'Data Regularization'!$O$2:$O$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AD2:AD11</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{9EA5C5F4-ED4A-42FF-B80A-46CD119E5CDA}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$O$2:$O$1048576</xm:f>
+            <xm:f>'Data Regularization'!$P$2:$P$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AE2:AE11</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D81C33F7-FD89-41B7-91B4-B2D71DD2AC1F}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$P$2:$P$1048576</xm:f>
+            <xm:f>'Data Regularization'!$Q$2:$Q$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AF2:AF11</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{1C91190D-6C3A-4134-9F97-823C25E2615B}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$C$2:$C$50</xm:f>
+            <xm:f>'Data Regularization'!$C$2:$C$29</xm:f>
           </x14:formula1>
           <xm:sqref>F2:F11</xm:sqref>
         </x14:dataValidation>
@@ -37117,12 +37489,6 @@
           </x14:formula1>
           <xm:sqref>E2:E11</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{3C3E11D3-993B-43FD-A727-064A9E0FE648}">
-          <x14:formula1>
-            <xm:f>'Data Regularization'!$P$2:$P$4</xm:f>
-          </x14:formula1>
-          <xm:sqref>AG2:AG11 AI2:AI11</xm:sqref>
-        </x14:dataValidation>
       </x14:dataValidations>
     </ext>
   </extLst>
@@ -37131,10 +37497,10 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E69DF24A-629E-47FA-8AA7-3395130DBEF2}">
-  <dimension ref="A1:AH7"/>
+  <dimension ref="A1:AI14"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
-    <row r="1" spans="1:34" s="1" customFormat="1" ht="29">
+    <row r="1" spans="1:35" s="1" customFormat="1" ht="29">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -37190,52 +37556,55 @@
         <v>364</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="U1" s="1" t="s">
         <v>367</v>
       </c>
       <c r="V1" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="W1" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="2" spans="1:34" ht="29">
+    <row r="2" spans="1:35" ht="29">
       <c r="A2" t="s">
         <v>120</v>
       </c>
@@ -37246,7 +37615,7 @@
         <v>189</v>
       </c>
       <c r="G2" t="s">
-        <v>401</v>
+        <v>503</v>
       </c>
       <c r="H2" s="7" t="s">
         <v>374</v>
@@ -37262,15 +37631,17 @@
       <c r="Q2" s="7"/>
       <c r="R2" s="7"/>
       <c r="S2" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T2" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U2" s="7" t="s">
         <v>371</v>
       </c>
-      <c r="V2" s="7"/>
+      <c r="V2" s="7" t="s">
+        <v>502</v>
+      </c>
       <c r="W2" s="7"/>
       <c r="X2" s="7"/>
       <c r="Y2" s="7"/>
@@ -37279,44 +37650,133 @@
       <c r="AB2" s="7"/>
       <c r="AC2" s="7"/>
       <c r="AD2" s="7"/>
-      <c r="AE2" t="s">
-        <v>19</v>
-      </c>
+      <c r="AE2" s="7"/>
       <c r="AF2" t="s">
+        <v>19</v>
+      </c>
+      <c r="AG2" t="s">
         <v>20</v>
       </c>
-      <c r="AH2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:34">
+      <c r="AI2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:35">
       <c r="D5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="E5">
         <f>COUNTIF(U:U, "Harmonizing")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34">
+    <row r="6" spans="1:35">
       <c r="D6" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="E6">
         <f>COUNTIF(U:U, "Disharmonizing")</f>
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34">
+    <row r="7" spans="1:35">
       <c r="D7" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E7">
         <f>E5/(E5+E6)</f>
         <v>0</v>
       </c>
     </row>
+    <row r="10" spans="1:35">
+      <c r="E10" s="11" t="s">
+        <v>504</v>
+      </c>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+    </row>
+    <row r="11" spans="1:35">
+      <c r="E11" t="s">
+        <v>500</v>
+      </c>
+      <c r="F11" t="s">
+        <v>501</v>
+      </c>
+      <c r="G11" t="s">
+        <v>502</v>
+      </c>
+      <c r="H11" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="12" spans="1:35">
+      <c r="D12" t="s">
+        <v>479</v>
+      </c>
+      <c r="E12">
+        <f>COUNTIFS($U$2:$U$2,"Harmonizing",$V$2:$V$2,"forward") + COUNTIFS($U$2:$U$2,"Harmonizing",$V$2:$V$2,"both")</f>
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <f>COUNTIFS($U$2:$U$2,"Harmonizing",$V$2:$V$2,"backward") + COUNTIFS($U$2:$U$2,"Harmonizing",$V$2:$V$2,"both")</f>
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <f>COUNTIFS($U$2:$U$2,"Harmonizing",$V$2:$V$2,"both")</f>
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <f>COUNTIFS($U$2:$U$2,"Harmonizing",$V$2:$V$2,"both") + COUNTIFS($U$2:$U$2,"Harmonizing",$V$2:$V$2,"forward") + COUNTIFS($U$2:$U$2,"Harmonizing",$V$2:$V$2,"backward")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35">
+      <c r="D13" t="s">
+        <v>480</v>
+      </c>
+      <c r="E13">
+        <f>COUNTIFS($U$2:$U$2,"Disharmonizing",$V$2:$V$2,"forward") + COUNTIFS($U$2:$U$2,"Disharmonizing",$V$2:$V$2,"both")</f>
+        <v>1</v>
+      </c>
+      <c r="F13">
+        <f>COUNTIFS($U$2:$U$2,"Disharmonizing",$V$2:$V$2,"backward") + COUNTIFS($U$2:$U$2,"Disharmonizing",$V$2:$V$2,"both")</f>
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <f>COUNTIFS($U$2:$U$2,"Disharmonizing",$V$2:$V$2,"both")</f>
+        <v>1</v>
+      </c>
+      <c r="H13">
+        <f>COUNTIFS($U$2:$U$2,"Disharmonizing",$V$2:$V$2,"both") + COUNTIFS($U$2:$U$2,"Disharmonizing",$V$2:$V$2,"forward") + COUNTIFS($U$2:$U$2,"Disharmonizing",$V$2:$V$2,"backward")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35">
+      <c r="D14" t="s">
+        <v>481</v>
+      </c>
+      <c r="E14">
+        <f>E12/(E12+E13)</f>
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <f t="shared" ref="F14:H14" si="0">F12/(F12+F13)</f>
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="E10:H10"/>
+  </mergeCells>
   <conditionalFormatting sqref="H2">
     <cfRule type="expression" dxfId="172" priority="4">
       <formula>$J2&lt;&gt;""</formula>
@@ -37373,18 +37833,18 @@
       <formula>"&lt;&gt;AND(LEFT($J2,3)=""Sub"", RIGHT($J2,4)&lt;&gt;""Form"")"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U2">
+  <conditionalFormatting sqref="U2:V2">
     <cfRule type="expression" dxfId="158" priority="7">
-      <formula>AND($W2&lt;&gt;"",OR($AD2="Yes",$AE2&lt;&gt;""))</formula>
+      <formula>AND($X2&lt;&gt;"",OR($AE2="Yes",$AF2&lt;&gt;""))</formula>
     </cfRule>
     <cfRule type="expression" dxfId="157" priority="8">
-      <formula>OR($AD2="Yes",$AE2&lt;&gt;"")</formula>
+      <formula>OR($AE2="Yes",$AF2&lt;&gt;"")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="156" priority="22">
-      <formula>AND($AD2&lt;&gt;"Yes",$AE2="")</formula>
+      <formula>AND($AE2&lt;&gt;"Yes",$AF2="")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U2:AD2">
+  <conditionalFormatting sqref="U2:AE2">
     <cfRule type="expression" dxfId="155" priority="20">
       <formula>AND($J2&lt;&gt;"",$J2&lt;&gt;"Unclear due to correction")</formula>
     </cfRule>
@@ -37392,32 +37852,44 @@
       <formula>OR($J2="",$J2="Unclear due to correction")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V2">
+  <conditionalFormatting sqref="W2">
     <cfRule type="expression" dxfId="153" priority="6">
-      <formula>AND($J2&lt;&gt;"",$J2&lt;&gt;"Unclear due to correction",$X2="")</formula>
+      <formula>AND($J2&lt;&gt;"",$J2&lt;&gt;"Unclear due to correction",$Y2="")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="W2">
+  <conditionalFormatting sqref="X2">
     <cfRule type="expression" dxfId="152" priority="9">
-      <formula>AND($X2="Yes",$Y2="")</formula>
+      <formula>AND($Y2="Yes",$Z2="")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="151" priority="10">
-      <formula>$X2=""</formula>
+      <formula>$Y2=""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AB2">
+  <conditionalFormatting sqref="AC2">
     <cfRule type="expression" dxfId="150" priority="23">
-      <formula>AND(OR($AB2&lt;&gt;"",$AC2&lt;&gt;""),$AD2="")</formula>
+      <formula>AND(OR($AC2&lt;&gt;"",$AD2&lt;&gt;""),$AE2="")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showInputMessage="1" sqref="V2" xr:uid="{9420346E-D036-4A6A-AB11-8368E6A31B8D}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" sqref="W2" xr:uid="{9420346E-D036-4A6A-AB11-8368E6A31B8D}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="15">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="16">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{A2F994F9-C529-42E4-A73E-18ADA3B0DC82}">
+          <x14:formula1>
+            <xm:f>'Data Regularization'!$Q$2:$Q$4</xm:f>
+          </x14:formula1>
+          <xm:sqref>AF2 AH2</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B40440AB-CA78-48F5-B352-BF34D132545E}">
+          <x14:formula1>
+            <xm:f>'Data Regularization'!$I$2:$I$5</xm:f>
+          </x14:formula1>
+          <xm:sqref>V2</xm:sqref>
+        </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{0AC256D2-616F-4FE1-8B14-C5C3CB107CB0}">
           <x14:formula1>
             <xm:f>'Data Regularization'!$D$2:$D$1048576</xm:f>
@@ -37444,49 +37916,49 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{78FFF3EE-149F-4F9D-A515-97D34C2CBD7E}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$J$2:$J$1048576</xm:f>
+            <xm:f>'Data Regularization'!$K$2:$K$1048576</xm:f>
           </x14:formula1>
-          <xm:sqref>U2 W2</xm:sqref>
+          <xm:sqref>X2 U2</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{523A2AF6-7AD3-4643-A9A3-C0052A67298C}">
-          <x14:formula1>
-            <xm:f>'Data Regularization'!$K$2:$K$1048576</xm:f>
-          </x14:formula1>
-          <xm:sqref>X2</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{9C5A799C-308D-45F3-A550-F2589D91FC4D}">
           <x14:formula1>
             <xm:f>'Data Regularization'!$L$2:$L$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>Y2</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{9A04F291-A209-4CA9-BD1C-028792C1D583}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{9C5A799C-308D-45F3-A550-F2589D91FC4D}">
           <x14:formula1>
             <xm:f>'Data Regularization'!$M$2:$M$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>Z2</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D74E094A-350F-4D3B-ABC7-5ABFDC491BD0}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{9A04F291-A209-4CA9-BD1C-028792C1D583}">
           <x14:formula1>
             <xm:f>'Data Regularization'!$N$2:$N$1048576</xm:f>
           </x14:formula1>
-          <xm:sqref>AB2</xm:sqref>
+          <xm:sqref>AA2</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{EF27BA90-7A55-4F50-B4B8-44E70763CC57}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D74E094A-350F-4D3B-ABC7-5ABFDC491BD0}">
           <x14:formula1>
             <xm:f>'Data Regularization'!$O$2:$O$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AC2</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C16CE901-FC33-4766-8585-C681470CF1BB}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{EF27BA90-7A55-4F50-B4B8-44E70763CC57}">
           <x14:formula1>
             <xm:f>'Data Regularization'!$P$2:$P$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AD2</xm:sqref>
         </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C16CE901-FC33-4766-8585-C681470CF1BB}">
+          <x14:formula1>
+            <xm:f>'Data Regularization'!$Q$2:$Q$1048576</xm:f>
+          </x14:formula1>
+          <xm:sqref>AE2</xm:sqref>
+        </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{87D8A66D-0DF7-48F9-B8A6-71E82D912DE2}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$C$2:$C$50</xm:f>
+            <xm:f>'Data Regularization'!$C$2:$C$29</xm:f>
           </x14:formula1>
           <xm:sqref>F2</xm:sqref>
         </x14:dataValidation>
@@ -37501,12 +37973,6 @@
             <xm:f>'Data Regularization'!$B$2:$B$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>E2</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{A2F994F9-C529-42E4-A73E-18ADA3B0DC82}">
-          <x14:formula1>
-            <xm:f>'Data Regularization'!$P$2:$P$4</xm:f>
-          </x14:formula1>
-          <xm:sqref>AE2 AG2</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -37575,10 +38041,10 @@
         <v>364</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="T1" s="1" t="s">
         <v>367</v>
@@ -37658,10 +38124,10 @@
       </c>
       <c r="Q2" s="7"/>
       <c r="R2" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S2" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T2" s="7"/>
       <c r="U2" s="7"/>
@@ -37717,10 +38183,10 @@
       </c>
       <c r="Q3" s="7"/>
       <c r="R3" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S3" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T3" s="7"/>
       <c r="U3" s="7"/>
@@ -37776,10 +38242,10 @@
       </c>
       <c r="Q4" s="7"/>
       <c r="R4" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S4" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T4" s="7"/>
       <c r="U4" s="7"/>
@@ -37890,10 +38356,10 @@
       </c>
       <c r="Q6" s="7"/>
       <c r="R6" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S6" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T6" s="7"/>
       <c r="U6" s="7"/>
@@ -37945,10 +38411,10 @@
         <v>326</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="N7" s="8" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="O7" s="7"/>
       <c r="P7" s="7">
@@ -37956,10 +38422,10 @@
       </c>
       <c r="Q7" s="7"/>
       <c r="R7" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S7" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T7" s="7"/>
       <c r="U7" s="7"/>
@@ -38066,10 +38532,10 @@
       </c>
       <c r="Q9" s="7"/>
       <c r="R9" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S9" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T9" s="7"/>
       <c r="U9" s="7"/>
@@ -38115,10 +38581,10 @@
       <c r="P10" s="7"/>
       <c r="Q10" s="7"/>
       <c r="R10" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S10" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T10" s="7"/>
       <c r="U10" s="7"/>
@@ -38174,10 +38640,10 @@
       </c>
       <c r="Q11" s="7"/>
       <c r="R11" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S11" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T11" s="7"/>
       <c r="U11" s="7"/>
@@ -38226,10 +38692,10 @@
       <c r="P12" s="7"/>
       <c r="Q12" s="7"/>
       <c r="R12" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S12" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T12" s="7"/>
       <c r="U12" s="7"/>
@@ -38290,10 +38756,10 @@
       </c>
       <c r="Q13" s="7"/>
       <c r="R13" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S13" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T13" s="7"/>
       <c r="U13" s="7"/>
@@ -38349,10 +38815,10 @@
       </c>
       <c r="Q14" s="7"/>
       <c r="R14" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S14" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T14" s="7"/>
       <c r="U14" s="7"/>
@@ -38410,10 +38876,10 @@
       </c>
       <c r="Q15" s="7"/>
       <c r="R15" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S15" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T15" s="7"/>
       <c r="U15" s="7"/>
@@ -38469,10 +38935,10 @@
       </c>
       <c r="Q16" s="7"/>
       <c r="R16" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S16" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T16" s="7"/>
       <c r="U16" s="7"/>
@@ -38494,7 +38960,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:33" ht="58">
+    <row r="17" spans="1:33" ht="72.5">
       <c r="A17" t="s">
         <v>89</v>
       </c>
@@ -38528,10 +38994,10 @@
       </c>
       <c r="Q17" s="7"/>
       <c r="R17" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S17" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T17" s="7"/>
       <c r="U17" s="7"/>
@@ -38577,10 +39043,10 @@
       <c r="P18" s="7"/>
       <c r="Q18" s="7"/>
       <c r="R18" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S18" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T18" s="7"/>
       <c r="U18" s="7"/>
@@ -38602,7 +39068,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:33" ht="275.5">
+    <row r="19" spans="1:33" ht="290">
       <c r="A19" t="s">
         <v>99</v>
       </c>
@@ -38641,10 +39107,10 @@
       </c>
       <c r="Q19" s="7"/>
       <c r="R19" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S19" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T19" s="7"/>
       <c r="U19" s="7"/>
@@ -38693,10 +39159,10 @@
       <c r="P20" s="7"/>
       <c r="Q20" s="7"/>
       <c r="R20" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S20" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T20" s="7"/>
       <c r="U20" s="7"/>
@@ -38752,10 +39218,10 @@
       </c>
       <c r="Q21" s="7"/>
       <c r="R21" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S21" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T21" s="7"/>
       <c r="U21" s="7"/>
@@ -38811,10 +39277,10 @@
       </c>
       <c r="Q22" s="7"/>
       <c r="R22" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S22" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T22" s="7"/>
       <c r="U22" s="7"/>
@@ -38860,10 +39326,10 @@
       <c r="P23" s="7"/>
       <c r="Q23" s="7"/>
       <c r="R23" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S23" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T23" s="7" t="s">
         <v>371</v>
@@ -38887,7 +39353,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:33" ht="145">
+    <row r="24" spans="1:33" ht="159.5">
       <c r="A24" t="s">
         <v>125</v>
       </c>
@@ -38921,10 +39387,10 @@
       <c r="P24" s="7"/>
       <c r="Q24" s="7"/>
       <c r="R24" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S24" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T24" s="7"/>
       <c r="U24" s="7"/>
@@ -39034,10 +39500,10 @@
       </c>
       <c r="Q26" s="7"/>
       <c r="R26" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S26" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T26" s="7"/>
       <c r="U26" s="7"/>
@@ -39093,10 +39559,10 @@
       </c>
       <c r="Q27" s="7"/>
       <c r="R27" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S27" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T27" s="7"/>
       <c r="U27" s="7"/>
@@ -39152,10 +39618,10 @@
       </c>
       <c r="Q28" s="7"/>
       <c r="R28" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S28" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T28" s="7"/>
       <c r="U28" s="7"/>
@@ -39201,10 +39667,10 @@
       <c r="P29" s="7"/>
       <c r="Q29" s="7"/>
       <c r="R29" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S29" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T29" s="7"/>
       <c r="U29" s="7"/>
@@ -39226,7 +39692,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:33" ht="58">
+    <row r="30" spans="1:33" ht="72.5">
       <c r="A30" t="s">
         <v>152</v>
       </c>
@@ -39263,10 +39729,10 @@
       </c>
       <c r="Q30" s="7"/>
       <c r="R30" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S30" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T30" s="7"/>
       <c r="U30" s="7"/>
@@ -39312,10 +39778,10 @@
       <c r="P31" s="7"/>
       <c r="Q31" s="7"/>
       <c r="R31" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="S31" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T31" s="7"/>
       <c r="U31" s="7"/>
@@ -39441,7 +39907,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="15">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{6F5C8BED-B3A9-411B-BE0E-0F4EA32A3DAB}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$P$2:$P$4</xm:f>
+            <xm:f>'Data Regularization'!$Q$2:$Q$4</xm:f>
           </x14:formula1>
           <xm:sqref>AD2:AD31 AF2:AF31</xm:sqref>
         </x14:dataValidation>
@@ -39459,49 +39925,49 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{39C1CDD8-C493-415A-B44B-F6556B18E11F}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$C$2:$C$50</xm:f>
+            <xm:f>'Data Regularization'!$C$2:$C$29</xm:f>
           </x14:formula1>
           <xm:sqref>F2:F31</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{50F251A5-2E54-4CAB-BC24-D5C1B4833079}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$P$2:$P$1048576</xm:f>
+            <xm:f>'Data Regularization'!$Q$2:$Q$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AC2:AC31</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{82C6ED36-3067-4AE1-9F85-E7267E23C1DB}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$O$2:$O$1048576</xm:f>
+            <xm:f>'Data Regularization'!$P$2:$P$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AB2:AB31</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{E25A2D63-3B80-4CD5-8163-F93987407460}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$N$2:$N$1048576</xm:f>
+            <xm:f>'Data Regularization'!$O$2:$O$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AA2:AA31</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{EB1EA456-5256-49F1-BB59-8817D065A90B}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$M$2:$M$1048576</xm:f>
+            <xm:f>'Data Regularization'!$N$2:$N$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>Y2:Y31</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{E15E5B01-AE41-461D-B5BE-FD93DAB80EE9}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$L$2:$L$1048576</xm:f>
+            <xm:f>'Data Regularization'!$M$2:$M$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>X2:X31</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D9847B75-F7A4-4EAC-B269-CD4E45ECC3B0}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$K$2:$K$1048576</xm:f>
+            <xm:f>'Data Regularization'!$L$2:$L$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>W2:W31</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{8011CF1D-A52D-42F2-BAE3-811A95C3921C}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$J$2:$J$1048576</xm:f>
+            <xm:f>'Data Regularization'!$K$2:$K$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>T2:T31 V2:V31</xm:sqref>
         </x14:dataValidation>
@@ -39590,16 +40056,16 @@
         <v>363</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="R1" s="1" t="s">
         <v>364</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="U1" s="1" t="s">
         <v>367</v>
@@ -39682,10 +40148,10 @@
       </c>
       <c r="R2" s="7"/>
       <c r="S2" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T2" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U2" s="7"/>
       <c r="V2" s="7"/>
@@ -39744,10 +40210,10 @@
       </c>
       <c r="R3" s="7"/>
       <c r="S3" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T3" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U3" s="7"/>
       <c r="V3" s="7"/>
@@ -39806,10 +40272,10 @@
       </c>
       <c r="R4" s="7"/>
       <c r="S4" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T4" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U4" s="7"/>
       <c r="V4" s="7"/>
@@ -39872,10 +40338,10 @@
       </c>
       <c r="R5" s="7"/>
       <c r="S5" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T5" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U5" s="7"/>
       <c r="V5" s="7"/>
@@ -39927,10 +40393,10 @@
         <v>326</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="N6" s="8" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="O6" s="7"/>
       <c r="P6" s="7">
@@ -39941,10 +40407,10 @@
       </c>
       <c r="R6" s="7"/>
       <c r="S6" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T6" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U6" s="7"/>
       <c r="V6" s="7"/>
@@ -40003,10 +40469,10 @@
       </c>
       <c r="R7" s="7"/>
       <c r="S7" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T7" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U7" s="7"/>
       <c r="V7" s="7"/>
@@ -40065,10 +40531,10 @@
       </c>
       <c r="R8" s="7"/>
       <c r="S8" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T8" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U8" s="7"/>
       <c r="V8" s="7"/>
@@ -40132,10 +40598,10 @@
       </c>
       <c r="R9" s="7"/>
       <c r="S9" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T9" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U9" s="7"/>
       <c r="V9" s="7"/>
@@ -40194,10 +40660,10 @@
       </c>
       <c r="R10" s="7"/>
       <c r="S10" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T10" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U10" s="7"/>
       <c r="V10" s="7"/>
@@ -40258,10 +40724,10 @@
       </c>
       <c r="R11" s="7"/>
       <c r="S11" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T11" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U11" s="7"/>
       <c r="V11" s="7"/>
@@ -40320,10 +40786,10 @@
       </c>
       <c r="R12" s="7"/>
       <c r="S12" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T12" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U12" s="7"/>
       <c r="V12" s="7"/>
@@ -40345,7 +40811,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:34" ht="58">
+    <row r="13" spans="1:34" ht="72.5">
       <c r="A13" t="s">
         <v>89</v>
       </c>
@@ -40382,10 +40848,10 @@
       </c>
       <c r="R13" s="7"/>
       <c r="S13" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T13" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U13" s="7"/>
       <c r="V13" s="7"/>
@@ -40407,7 +40873,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:34" ht="275.5">
+    <row r="14" spans="1:34" ht="290">
       <c r="A14" t="s">
         <v>99</v>
       </c>
@@ -40449,10 +40915,10 @@
       </c>
       <c r="R14" s="7"/>
       <c r="S14" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T14" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U14" s="7"/>
       <c r="V14" s="7"/>
@@ -40511,10 +40977,10 @@
       </c>
       <c r="R15" s="7"/>
       <c r="S15" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T15" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U15" s="7"/>
       <c r="V15" s="7"/>
@@ -40573,10 +41039,10 @@
       </c>
       <c r="R16" s="7"/>
       <c r="S16" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T16" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U16" s="7"/>
       <c r="V16" s="7"/>
@@ -40598,7 +41064,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:34" ht="145">
+    <row r="17" spans="1:34" ht="159.5">
       <c r="A17" t="s">
         <v>125</v>
       </c>
@@ -40631,14 +41097,14 @@
       <c r="O17" s="7"/>
       <c r="P17" s="7"/>
       <c r="Q17" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="R17" s="7"/>
       <c r="S17" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T17" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U17" s="7"/>
       <c r="V17" s="7"/>
@@ -40697,10 +41163,10 @@
       </c>
       <c r="R18" s="7"/>
       <c r="S18" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T18" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U18" s="7"/>
       <c r="V18" s="7"/>
@@ -40759,10 +41225,10 @@
       </c>
       <c r="R19" s="7"/>
       <c r="S19" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T19" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U19" s="7"/>
       <c r="V19" s="7"/>
@@ -40821,10 +41287,10 @@
       </c>
       <c r="R20" s="7"/>
       <c r="S20" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T20" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U20" s="7"/>
       <c r="V20" s="7"/>
@@ -40846,7 +41312,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:34" ht="58">
+    <row r="21" spans="1:34" ht="72.5">
       <c r="A21" t="s">
         <v>152</v>
       </c>
@@ -40886,10 +41352,10 @@
       </c>
       <c r="R21" s="7"/>
       <c r="S21" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T21" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U21" s="7"/>
       <c r="V21" s="7"/>
@@ -40913,7 +41379,7 @@
     </row>
     <row r="24" spans="1:34">
       <c r="E24" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="F24">
         <f>COUNTIF(G:G,"Addition")</f>
@@ -40922,13 +41388,13 @@
     </row>
     <row r="25" spans="1:34">
       <c r="B25" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C25" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E25" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F25">
         <f>COUNTIF(G:G,"Omission")</f>
@@ -40943,7 +41409,7 @@
         <v>325</v>
       </c>
       <c r="E26" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F26">
         <f>F24/(F24+F25)</f>
@@ -40974,7 +41440,7 @@
         <v>352</v>
       </c>
       <c r="E29" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F29">
         <f>COUNTIFS(G:G,"Addition", K:K,"Article")+COUNTIFS(G:G,"Addition", K:K,"Conjunction")+COUNTIFS(G:G,"Addition", K:K,"Pronoun")+COUNTIFS(G:G,"Addition", K:K,"Preposition")+COUNTIFS(G:G,"Addition", K:K,"Particle")+COUNTIFS(G:G,"Addition", K:K,"Vocative")</f>
@@ -40989,7 +41455,7 @@
         <v>383</v>
       </c>
       <c r="E30" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F30">
         <f>COUNTIFS(G:G,"Omission", K:K,"Article")+COUNTIFS(G:G,"Omission", K:K,"Conjunction")+COUNTIFS(G:G,"Omission", K:K,"Pronoun")+COUNTIFS(G:G,"Omission", K:K,"Preposition")+COUNTIFS(G:G,"Omission", K:K,"Particle")+COUNTIFS(G:G,"Omission", K:K,"Vocative")</f>
@@ -41001,7 +41467,7 @@
         <v>353</v>
       </c>
       <c r="E31" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F31">
         <f>F29/(F29+F30)</f>
@@ -41010,7 +41476,7 @@
     </row>
     <row r="34" spans="3:6">
       <c r="E34" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F34">
         <f>COUNTIFS(G:G,"Addition", K:K,"Adjective")+COUNTIFS(G:G,"Addition", K:K,"Adverb")+COUNTIFS(G:G,"Addition", K:K,"Noun")+COUNTIFS(G:G,"Addition", K:K,"Participle")+COUNTIFS(G:G,"Addition", K:K,"Verb")</f>
@@ -41019,7 +41485,7 @@
     </row>
     <row r="35" spans="3:6">
       <c r="E35" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F35">
         <f>COUNTIFS(G:G,"Omission", K:K,"Adjective")+COUNTIFS(G:G,"Omission", K:K,"Adverb")+COUNTIFS(G:G,"Omission", K:K,"Noun")+COUNTIFS(G:G,"Omission", K:K,"Participle")+COUNTIFS(G:G,"Omission", K:K,"Verb")</f>
@@ -41028,7 +41494,7 @@
     </row>
     <row r="36" spans="3:6">
       <c r="E36" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="F36">
         <f>F34/(F34+F35)</f>
@@ -41037,7 +41503,7 @@
     </row>
     <row r="37" spans="3:6">
       <c r="E37" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="F37">
         <f>F36-F31</f>
@@ -41046,7 +41512,7 @@
     </row>
     <row r="40" spans="3:6">
       <c r="D40" s="11" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
@@ -41056,15 +41522,15 @@
         <v>326</v>
       </c>
       <c r="E41" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="F41" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="42" spans="3:6">
       <c r="C42" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D42">
         <f>COUNTIFS(G:G,"Addition", L:L, "Present")</f>
@@ -41081,7 +41547,7 @@
     </row>
     <row r="43" spans="3:6">
       <c r="C43" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D43">
         <f>COUNTIFS(G:G,"Omission", L:L, "Present")</f>
@@ -41098,7 +41564,7 @@
     </row>
     <row r="44" spans="3:6">
       <c r="C44" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D44">
         <f>SUM(D42+D43)</f>
@@ -41115,18 +41581,18 @@
     </row>
     <row r="47" spans="3:6">
       <c r="D47" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E47" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F47" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="48" spans="3:6">
       <c r="C48" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D48">
         <f>COUNTIFS(G:G,"Addition", L:L, "Absent")</f>
@@ -41143,7 +41609,7 @@
     </row>
     <row r="49" spans="3:6">
       <c r="C49" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D49">
         <f>COUNTIFS(G:G,"Addition", L:L, "Present")</f>
@@ -41160,7 +41626,7 @@
     </row>
     <row r="50" spans="3:6">
       <c r="E50" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="F50">
         <f>F49-F48</f>
@@ -41169,18 +41635,18 @@
     </row>
     <row r="53" spans="3:6">
       <c r="D53" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E53" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F53" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="54" spans="3:6">
       <c r="C54" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D54">
         <f>COUNTIFS(G:G,"Addition", O:O, "")</f>
@@ -41197,7 +41663,7 @@
     </row>
     <row r="55" spans="3:6">
       <c r="C55" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D55">
         <f>COUNTIFS(G:G,"Addition", O:O, "Dittography")</f>
@@ -41214,7 +41680,7 @@
     </row>
     <row r="56" spans="3:6">
       <c r="E56" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="F56">
         <f>F55-F54</f>
@@ -41223,16 +41689,16 @@
     </row>
     <row r="59" spans="3:6">
       <c r="C59" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D59" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E59" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F59" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="60" spans="3:6">
@@ -41254,7 +41720,7 @@
     </row>
     <row r="61" spans="3:6">
       <c r="C61" s="9" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D61">
         <f>COUNTIFS(G:G,"Addition", I:I, "&gt;=2", I:I, "&lt;=3")</f>
@@ -41271,7 +41737,7 @@
     </row>
     <row r="62" spans="3:6">
       <c r="C62" s="9" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D62">
         <f>COUNTIFS(G:G,"Addition", I:I, "&gt;=4")</f>
@@ -41288,16 +41754,16 @@
     </row>
     <row r="65" spans="3:6">
       <c r="C65" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D65" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E65" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F65" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="66" spans="3:6">
@@ -41370,7 +41836,7 @@
     </row>
     <row r="70" spans="3:6">
       <c r="C70" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D70" s="9">
         <f>COUNTIFS(G:G,"Addition", I:I, C70)</f>
@@ -41390,7 +41856,7 @@
     </row>
     <row r="73" spans="3:6">
       <c r="E73" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="F73">
         <v>20338</v>
@@ -41513,6 +41979,12 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="15">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{F1579A6B-EA05-448B-AB0A-D7BD3EB57CD0}">
+          <x14:formula1>
+            <xm:f>'Data Regularization'!$Q$2:$Q$4</xm:f>
+          </x14:formula1>
+          <xm:sqref>AG2:AG21 AE2:AE21</xm:sqref>
+        </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C63FC012-801B-4F8D-B157-6D25AC774B11}">
           <x14:formula1>
             <xm:f>'Data Regularization'!$D$2:$D$1048576</xm:f>
@@ -41539,49 +42011,49 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{97C80129-5444-41C6-BE28-E1C738A81594}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$J$2:$J$1048576</xm:f>
+            <xm:f>'Data Regularization'!$K$2:$K$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>W2:W21 U2:U21</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{4605543F-856B-4F87-925B-99EB3AC04FF2}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$K$2:$K$1048576</xm:f>
+            <xm:f>'Data Regularization'!$L$2:$L$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>X2:X21</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{745BB9B1-4E49-462E-A7E7-C8C8D8E922F3}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$L$2:$L$1048576</xm:f>
+            <xm:f>'Data Regularization'!$M$2:$M$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>Y2:Y21</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{26CA32CF-BDFA-468F-8E3C-754403BC1998}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$M$2:$M$1048576</xm:f>
+            <xm:f>'Data Regularization'!$N$2:$N$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>Z2:Z21</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{9307B292-7CD7-490C-AB4B-9E784730EE78}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$N$2:$N$1048576</xm:f>
+            <xm:f>'Data Regularization'!$O$2:$O$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AB2:AB21</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C373B66C-67AD-4086-BE04-BC17297F39EF}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$O$2:$O$1048576</xm:f>
+            <xm:f>'Data Regularization'!$P$2:$P$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AC2:AC21</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{0890046C-E70A-4E85-8AA5-3E3EEBEDCAAF}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$P$2:$P$1048576</xm:f>
+            <xm:f>'Data Regularization'!$Q$2:$Q$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AD2:AD21</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{83C975C5-F757-4A8B-9337-C4CBC21FD4B6}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$C$2:$C$50</xm:f>
+            <xm:f>'Data Regularization'!$C$2:$C$29</xm:f>
           </x14:formula1>
           <xm:sqref>F2:F21</xm:sqref>
         </x14:dataValidation>
@@ -41597,12 +42069,6 @@
           </x14:formula1>
           <xm:sqref>E2:E21</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{F1579A6B-EA05-448B-AB0A-D7BD3EB57CD0}">
-          <x14:formula1>
-            <xm:f>'Data Regularization'!$P$2:$P$4</xm:f>
-          </x14:formula1>
-          <xm:sqref>AG2:AG21 AE2:AE21</xm:sqref>
-        </x14:dataValidation>
       </x14:dataValidations>
     </ext>
   </extLst>
